--- a/implementaciones.xlsx
+++ b/implementaciones.xlsx
@@ -366,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J205"/>
+  <dimension ref="A1:J138"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="27.34375" customWidth="true"/>
@@ -412,7 +412,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Generated by Fernanda Durán on Jul 17, 2026 11:38 AM</t>
+          <t xml:space="preserve">    Generated by Fernanda Durán on Jul 28, 2026 12:05 AM</t>
         </is>
       </c>
       <c r="B3" s="5"/>
@@ -440,7 +440,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Record Count : 198</t>
+          <t xml:space="preserve">    Record Count : 131</t>
         </is>
       </c>
       <c r="B5" s="5"/>
@@ -520,7 +520,7 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>SEICA - BOBURHAM- GEOVICTORIA ASISTENCIA</t>
+          <t>Operadora Wing's Army, S.A. de C.V.</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -530,16 +530,16 @@
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t/>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>1. En Traspaso</t>
+          <t>0. Sin Asignar</t>
         </is>
       </c>
       <c r="E8" s="17" t="n">
-        <v>5499.0</v>
+        <v>50.0</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
@@ -553,7 +553,7 @@
       </c>
       <c r="H8" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
+          <t>Asistencia; Módulo de permisos; Módulo Vacaciones</t>
         </is>
       </c>
       <c r="I8" s="18" t="inlineStr">
@@ -563,14 +563,14 @@
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>SEICSA</t>
+          <t>Operadora Wing's Army, S.A. de C.V.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>IBL, Accesos</t>
+          <t>PC DE MÉXICO</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -580,16 +580,16 @@
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>Abandono</t>
+          <t>3. En Ejecución</t>
         </is>
       </c>
       <c r="E9" s="17" t="n">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
       </c>
       <c r="H9" s="16" t="inlineStr">
         <is>
-          <t>Acceso</t>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I9" s="18" t="inlineStr">
@@ -613,14 +613,14 @@
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>IBL VENTURE CAPITAL</t>
+          <t>PC de México</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>Soluciones en Mantenimiento Industrial MAQUI</t>
+          <t>BREMONT ARQUITECTOS</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E10" s="17" t="n">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
@@ -663,31 +663,33 @@
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>Soluciones en Mantenimiento Industrial MAQUI</t>
+          <t>BREMONT ARQUITECTOS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>CONSTRUCTORADEBASCULAS</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="n">
-        <v>0.0</v>
+          <t>Migración de usuarios Maximus</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>3. En Ejecución</t>
+          <t>1. En Traspaso</t>
         </is>
       </c>
       <c r="E11" s="17" t="n">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -711,14 +713,14 @@
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>CONSTRUCTORA DE BASCULAS</t>
+          <t>CORPORACION DE RESTAURANTES MAXIMUS SA DE CV</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Bodega de Papel Mesones, S.A. de C.V.</t>
+          <t>Think Tim</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -737,7 +739,7 @@
         </is>
       </c>
       <c r="E12" s="17" t="n">
-        <v>41.0</v>
+        <v>30.0</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
@@ -761,14 +763,14 @@
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>BODEGA DE PAPEL MESONES SA DE CV</t>
+          <t>Think Tim</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>Accesos interno y externos Softys Puebla</t>
+          <t>Migración vacaciones y permisos</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
@@ -783,11 +785,11 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>2. En Planificación</t>
+          <t>1. En Traspaso</t>
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>1270.0</v>
+        <v>1850.0</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
@@ -801,7 +803,7 @@
       </c>
       <c r="H13" s="16" t="inlineStr">
         <is>
-          <t>Acceso; Externos</t>
+          <t>Módulo de permisos; Módulo Vacaciones</t>
         </is>
       </c>
       <c r="I13" s="18" t="inlineStr">
@@ -811,18 +813,20 @@
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>Softys México</t>
+          <t>Office Max</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>ENTIA DE MÉXICO</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="n">
-        <v>0.0</v>
+          <t>Migración permisos y vacaciones</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
@@ -831,11 +835,11 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>2. En Planificación</t>
+          <t>1. En Traspaso</t>
         </is>
       </c>
       <c r="E14" s="17" t="n">
-        <v>338.0</v>
+        <v>800.0</v>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
@@ -849,7 +853,7 @@
       </c>
       <c r="H14" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
+          <t>Módulo de permisos; Módulo Vacaciones</t>
         </is>
       </c>
       <c r="I14" s="18" t="inlineStr">
@@ -859,14 +863,14 @@
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>ENTIA DE MEXICO SA DE CV</t>
+          <t>CONVERSE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>ARBOS</t>
+          <t>J&amp;T R1 Baja california</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -876,16 +880,16 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>3. En Ejecución</t>
+          <t>2. En Planificación</t>
         </is>
       </c>
       <c r="E15" s="17" t="n">
-        <v>20.0</v>
+        <v>175.0</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
@@ -909,14 +913,14 @@
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>Arbos</t>
+          <t>J&amp;T EXPRESS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Entia</t>
+          <t>SEICA - BOBURHAM- GEOVICTORIA ASISTENCIA</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
@@ -926,16 +930,16 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>1. En Traspaso</t>
         </is>
       </c>
       <c r="E16" s="17" t="n">
-        <v>338.0</v>
+        <v>5499.0</v>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
@@ -959,18 +963,20 @@
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>ENTIA DE MEXICO SA DE CV</t>
+          <t>SEICSA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>FORMEL D - ASISTENCIA</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="n">
-        <v>0.0</v>
+          <t>IBL, Accesos</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
@@ -979,11 +985,11 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>3. En Ejecución</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E17" s="17" t="n">
-        <v>20.0</v>
+        <v>11.0</v>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
@@ -997,39 +1003,43 @@
       </c>
       <c r="H17" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo de permisos; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>46219.0</v>
+          <t>Acceso</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>Formel D</t>
+          <t>IBL VENTURE CAPITAL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>Ancora, Asistencia y acceso</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="n">
-        <v>0.0</v>
+          <t>Soluciones en Mantenimiento Industrial MAQUI</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>3. En Ejecución</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E18" s="17" t="n">
-        <v>140.0</v>
+        <v>19.0</v>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
@@ -1043,22 +1053,24 @@
       </c>
       <c r="H18" s="16" t="inlineStr">
         <is>
-          <t>Acceso; Asistencia</t>
-        </is>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>46336.0</v>
+          <t>Asistencia</t>
+        </is>
+      </c>
+      <c r="I18" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>ANCORA</t>
+          <t>Soluciones en Mantenimiento Industrial MAQUI</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Xander Asistencia y Vacaciones</t>
+          <t>CONSTRUCTORADEBASCULAS</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1071,11 +1083,11 @@
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>3. En Ejecución</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E19" s="17" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
@@ -1089,7 +1101,7 @@
       </c>
       <c r="H19" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I19" s="18" t="inlineStr">
@@ -1099,22 +1111,24 @@
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>XANDER</t>
+          <t>CONSTRUCTORA DE BASCULAS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Implementación IPISA</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="n">
-        <v>0.0</v>
+          <t>Bodega de Papel Mesones, S.A. de C.V.</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
@@ -1123,7 +1137,7 @@
         </is>
       </c>
       <c r="E20" s="17" t="n">
-        <v>300.0</v>
+        <v>41.0</v>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
@@ -1137,26 +1151,30 @@
       </c>
       <c r="H20" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="n">
-        <v>46288.0</v>
+          <t>Asistencia</t>
+        </is>
+      </c>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>IPISA</t>
+          <t>BODEGA DE PAPEL MESONES SA DE CV</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>PIVACSA</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="n">
-        <v>0.0</v>
+          <t>Accesos interno y externos Softys Puebla</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
@@ -1165,14 +1183,16 @@
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>3. En Ejecución</t>
+          <t>2. En Planificación</t>
         </is>
       </c>
       <c r="E21" s="17" t="n">
-        <v>71.0</v>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>71.0</v>
+        <v>1270.0</v>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
@@ -1181,41 +1201,41 @@
       </c>
       <c r="H21" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="n">
-        <v>46296.0</v>
+          <t>Acceso; Externos</t>
+        </is>
+      </c>
+      <c r="I21" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>PIVACSA</t>
+          <t>Softys México</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>Xander Asistencia y Vacaciones</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>ENTIA DE MÉXICO</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n">
+        <v>0.0</v>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>3. En Ejecución</t>
         </is>
       </c>
       <c r="E22" s="17" t="n">
-        <v>12.0</v>
+        <v>338.0</v>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
@@ -1229,28 +1249,28 @@
       </c>
       <c r="H22" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia</t>
+        </is>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>46310.0</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>XANDER</t>
+          <t>ENTIA DE MEXICO SA DE CV</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>LOGISTICA Y TRANSPORTE EMPRESARIAL PEMI, SA DE CV</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="n">
-        <v>0.0</v>
+          <t>ARBOS</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
@@ -1259,14 +1279,16 @@
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>3. En Ejecución</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E23" s="17" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F23" s="17" t="n">
-        <v>6.0</v>
+        <v>20.0</v>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
@@ -1285,22 +1307,22 @@
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>Logistica y Transporte Empresarial PEMI</t>
+          <t>Arbos</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>Quality Cocinas y Closets</t>
+          <t>FORMEL D - ASISTENCIA</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
-        <v>26.67</v>
+        <v>0.0</v>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
@@ -1309,7 +1331,7 @@
         </is>
       </c>
       <c r="E24" s="17" t="n">
-        <v>14.0</v>
+        <v>20.0</v>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
@@ -1323,30 +1345,26 @@
       </c>
       <c r="H24" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I24" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia; Módulo de permisos; Módulo Vacaciones</t>
+        </is>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>46310.0</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>Quality Cocinas y Closets</t>
+          <t>Formel D</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>Migración Modulo de Vacaciones Logicamex</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Ancora, Asistencia y acceso</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n">
+        <v>0.0</v>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
@@ -1355,11 +1373,11 @@
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>2. En Planificación</t>
+          <t>3. En Ejecución</t>
         </is>
       </c>
       <c r="E25" s="17" t="n">
-        <v>101.0</v>
+        <v>140.0</v>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
@@ -1373,22 +1391,22 @@
       </c>
       <c r="H25" s="16" t="inlineStr">
         <is>
-          <t>Módulo Vacaciones</t>
+          <t>Acceso; Asistencia</t>
         </is>
       </c>
       <c r="I25" s="18" t="n">
-        <v>46232.0</v>
+        <v>46336.0</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>LOGISTICA COMERCIAL LOGICOM SA</t>
+          <t>ANCORA</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>Implementación Gao Aluminio - Asistencia</t>
+          <t>Xander Asistencia y Vacaciones</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1396,21 +1414,19 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>3. En Ejecución</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E26" s="17" t="n">
-        <v>310.0</v>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>12.0</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <v>12.0</v>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
@@ -1419,26 +1435,28 @@
       </c>
       <c r="H26" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I26" s="18" t="n">
-        <v>46338.0</v>
+          <t>Asistencia; Módulo Vacaciones</t>
+        </is>
+      </c>
+      <c r="I26" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>GAO Aluminio</t>
+          <t>XANDER</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>DGAS</t>
+          <t>Implementación IPISA</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
-        <v>93.75</v>
+        <v>0.0</v>
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
@@ -1451,10 +1469,12 @@
         </is>
       </c>
       <c r="E27" s="17" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="F27" s="17" t="n">
-        <v>16.0</v>
+        <v>300.0</v>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
@@ -1467,22 +1487,22 @@
         </is>
       </c>
       <c r="I27" s="18" t="n">
-        <v>46264.0</v>
+        <v>46288.0</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>DGAS</t>
+          <t>IPISA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>LINE SHOP MARKET</t>
+          <t>PIVACSA</t>
         </is>
       </c>
       <c r="B28" s="15" t="n">
-        <v>11.11</v>
+        <v>0.0</v>
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
@@ -1495,10 +1515,10 @@
         </is>
       </c>
       <c r="E28" s="17" t="n">
-        <v>20.0</v>
+        <v>71.0</v>
       </c>
       <c r="F28" s="17" t="n">
-        <v>18.0</v>
+        <v>71.0</v>
       </c>
       <c r="G28" s="16" t="inlineStr">
         <is>
@@ -1507,26 +1527,26 @@
       </c>
       <c r="H28" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo de permisos; Módulo Vacaciones</t>
+          <t>Asistencia; Módulo Vacaciones</t>
         </is>
       </c>
       <c r="I28" s="18" t="n">
-        <v>46274.0</v>
+        <v>46296.0</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>Lineshop</t>
+          <t>PIVACSA</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>Constructora IyAT</t>
+          <t>LOGISTICA Y TRANSPORTE EMPRESARIAL PEMI, SA DE CV</t>
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>66.67</v>
+        <v>0.0</v>
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
@@ -1535,16 +1555,14 @@
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>4. a) En Marcha Blanca (con pendientes)</t>
+          <t>3. En Ejecución</t>
         </is>
       </c>
       <c r="E29" s="17" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>6.0</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>6.0</v>
       </c>
       <c r="G29" s="16" t="inlineStr">
         <is>
@@ -1563,34 +1581,36 @@
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>Iyat</t>
+          <t>Logistica y Transporte Empresarial PEMI</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>GROSS ARQUITECTURA</t>
+          <t>Quality Cocinas y Closets</t>
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>45.71</v>
+        <v>26.67</v>
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>3. En Ejecución</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E30" s="17" t="n">
-        <v>70.0</v>
-      </c>
-      <c r="F30" s="17" t="n">
-        <v>70.0</v>
+        <v>14.0</v>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
@@ -1599,22 +1619,24 @@
       </c>
       <c r="H30" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I30" s="18" t="n">
-        <v>46303.0</v>
+          <t>Asistencia</t>
+        </is>
+      </c>
+      <c r="I30" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>Gross arquitectura</t>
+          <t>Quality Cocinas y Closets</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Implementación IPISA</t>
+          <t>Migración Modulo de Vacaciones Logicamex</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
@@ -1624,16 +1646,16 @@
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>2. En Planificación</t>
         </is>
       </c>
       <c r="E31" s="17" t="n">
-        <v>300.0</v>
+        <v>101.0</v>
       </c>
       <c r="F31" s="17" t="inlineStr">
         <is>
@@ -1647,43 +1669,39 @@
       </c>
       <c r="H31" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I31" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Módulo Vacaciones</t>
+        </is>
+      </c>
+      <c r="I31" s="18" t="n">
+        <v>46232.0</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>IPISA</t>
+          <t>LOGISTICA COMERCIAL LOGICOM SA</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>GROSS ARQUITECTURA</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Implementación Gao Aluminio - Asistencia</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="n">
+        <v>0.0</v>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>3. En Ejecución</t>
         </is>
       </c>
       <c r="E32" s="17" t="n">
-        <v>70.0</v>
+        <v>310.0</v>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
@@ -1697,28 +1715,26 @@
       </c>
       <c r="H32" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I32" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia</t>
+        </is>
+      </c>
+      <c r="I32" s="18" t="n">
+        <v>46338.0</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>Gross arquitectura</t>
+          <t>GAO Aluminio</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>GRUPO COCINA MEXICANA</t>
+          <t>DGAS</t>
         </is>
       </c>
       <c r="B33" s="15" t="n">
-        <v>14.29</v>
+        <v>93.75</v>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
@@ -1731,38 +1747,38 @@
         </is>
       </c>
       <c r="E33" s="17" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="F33" s="17" t="n">
-        <v>6.0</v>
+        <v>16.0</v>
       </c>
       <c r="G33" s="16" t="inlineStr">
         <is>
-          <t>Tadá México</t>
+          <t/>
         </is>
       </c>
       <c r="H33" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
+          <t>Asistencia; Módulo Vacaciones</t>
         </is>
       </c>
       <c r="I33" s="18" t="n">
-        <v>46324.0</v>
+        <v>46264.0</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>Grupo Cocina Mexicana</t>
+          <t>DGAS</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>ZKC ADMINISTRACION SAPI DE CV</t>
+          <t>LINE SHOP MARKET</t>
         </is>
       </c>
       <c r="B34" s="15" t="n">
-        <v>4.17</v>
+        <v>11.11</v>
       </c>
       <c r="C34" s="16" t="inlineStr">
         <is>
@@ -1775,12 +1791,10 @@
         </is>
       </c>
       <c r="E34" s="17" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>20.0</v>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>18.0</v>
       </c>
       <c r="G34" s="16" t="inlineStr">
         <is>
@@ -1793,42 +1807,38 @@
         </is>
       </c>
       <c r="I34" s="18" t="n">
-        <v>46275.0</v>
+        <v>46274.0</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>ZKC</t>
+          <t>Lineshop</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>Implementacion Peckers</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>GROSS ARQUITECTURA</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="n">
+        <v>45.71</v>
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>3. En Ejecución</t>
         </is>
       </c>
       <c r="E35" s="17" t="n">
-        <v>36.0</v>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>70.0</v>
+      </c>
+      <c r="F35" s="17" t="n">
+        <v>70.0</v>
       </c>
       <c r="G35" s="16" t="inlineStr">
         <is>
@@ -1837,30 +1847,26 @@
       </c>
       <c r="H35" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I35" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia; Módulo Vacaciones</t>
+        </is>
+      </c>
+      <c r="I35" s="18" t="n">
+        <v>46303.0</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>PECKERS</t>
+          <t>Gross arquitectura</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>ASTROLLANTAS</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>GRUPO COCINA MEXICANA</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="n">
+        <v>14.29</v>
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
@@ -1869,20 +1875,18 @@
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>Detenida</t>
+          <t>3. En Ejecución</t>
         </is>
       </c>
       <c r="E36" s="17" t="n">
-        <v>168.0</v>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>5.0</v>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>6.0</v>
       </c>
       <c r="G36" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Tadá México</t>
         </is>
       </c>
       <c r="H36" s="16" t="inlineStr">
@@ -1895,20 +1899,18 @@
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>ASTROLLANTAS MÉXICO</t>
+          <t>Grupo Cocina Mexicana</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>Implementacion Dicka</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>ZKC ADMINISTRACION SAPI DE CV</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n">
+        <v>4.17</v>
       </c>
       <c r="C37" s="16" t="inlineStr">
         <is>
@@ -1917,11 +1919,11 @@
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>Detenida</t>
+          <t>3. En Ejecución</t>
         </is>
       </c>
       <c r="E37" s="17" t="n">
-        <v>1409.0</v>
+        <v>24.0</v>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
@@ -1935,24 +1937,22 @@
       </c>
       <c r="H37" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Dashboard; Reporte a medida (RAM)</t>
-        </is>
-      </c>
-      <c r="I37" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia; Módulo de permisos; Módulo Vacaciones</t>
+        </is>
+      </c>
+      <c r="I37" s="18" t="n">
+        <v>46275.0</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>DICKA LOGISTICS</t>
+          <t>ZKC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Implementacion Peckers</t>
+          <t>ASTROLLANTAS</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
@@ -1962,16 +1962,16 @@
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Detenida</t>
         </is>
       </c>
       <c r="E38" s="17" t="n">
-        <v>35.0</v>
+        <v>168.0</v>
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
@@ -1988,21 +1988,19 @@
           <t>Asistencia</t>
         </is>
       </c>
-      <c r="I38" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="I38" s="18" t="n">
+        <v>46324.0</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>PECKERS</t>
+          <t>ASTROLLANTAS MÉXICO</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Implementación WeeMedic</t>
+          <t>Implementacion Dicka</t>
         </is>
       </c>
       <c r="B39" s="15" t="inlineStr">
@@ -2021,12 +2019,10 @@
         </is>
       </c>
       <c r="E39" s="17" t="n">
-        <v>270.0</v>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>1409.0</v>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>1405.0</v>
       </c>
       <c r="G39" s="16" t="inlineStr">
         <is>
@@ -2035,26 +2031,28 @@
       </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
-          <t>Acceso; Asistencia</t>
+          <t>Asistencia; Dashboard; Reporte a medida (RAM)</t>
         </is>
       </c>
       <c r="I39" s="18" t="n">
-        <v>46331.0</v>
+        <v>46300.0</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>WeeMedic</t>
+          <t>DICKA LOGISTICS</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Implementación J&amp;T EXPRESS METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="n">
-        <v>43.92</v>
+          <t>Implementación WeeMedic</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C40" s="16" t="inlineStr">
         <is>
@@ -2067,10 +2065,12 @@
         </is>
       </c>
       <c r="E40" s="17" t="n">
-        <v>568.0</v>
-      </c>
-      <c r="F40" s="17" t="n">
-        <v>575.0</v>
+        <v>270.0</v>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G40" s="16" t="inlineStr">
         <is>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="H40" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
+          <t>Acceso; Asistencia</t>
         </is>
       </c>
       <c r="I40" s="18" t="n">
-        <v>46267.0</v>
+        <v>46331.0</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>J&amp;T EXPRESS</t>
+          <t>WeeMedic</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Clinica Pacífica</t>
+          <t>Implementación J&amp;T EXPRESS METROPOLITANA</t>
         </is>
       </c>
       <c r="B41" s="15" t="n">
-        <v>93.33</v>
+        <v>43.92</v>
       </c>
       <c r="C41" s="16" t="inlineStr">
         <is>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="E41" s="17" t="n">
-        <v>30.0</v>
+        <v>568.0</v>
       </c>
       <c r="F41" s="17" t="n">
-        <v>30.0</v>
+        <v>575.0</v>
       </c>
       <c r="G41" s="16" t="inlineStr">
         <is>
@@ -2123,28 +2123,26 @@
       </c>
       <c r="H41" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo de permisos; Módulo Vacaciones</t>
+          <t>Asistencia; Módulo Vacaciones</t>
         </is>
       </c>
       <c r="I41" s="18" t="n">
-        <v>46275.0</v>
+        <v>46267.0</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>Clinica Pacífica</t>
+          <t>J&amp;T EXPRESS</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>Plan georetail Enterprise - asistencia, vacaciones, dashboard, victoria, alertas, optimizador</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Clinica Pacífica</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="n">
+        <v>93.33</v>
       </c>
       <c r="C42" s="16" t="inlineStr">
         <is>
@@ -2153,16 +2151,14 @@
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>Detenida</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E42" s="17" t="n">
-        <v>500.0</v>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>30.0</v>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>30.0</v>
       </c>
       <c r="G42" s="16" t="inlineStr">
         <is>
@@ -2171,28 +2167,28 @@
       </c>
       <c r="H42" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Dashboard; Integración Estándar; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I42" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia; Módulo de permisos; Módulo Vacaciones</t>
+        </is>
+      </c>
+      <c r="I42" s="18" t="n">
+        <v>46275.0</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>El Papalote</t>
+          <t>Clinica Pacífica</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>Implementación - Asistencia - PTIQCS</t>
-        </is>
-      </c>
-      <c r="B43" s="15" t="n">
-        <v>85.71</v>
+          <t>Plan georetail Enterprise - asistencia, vacaciones, dashboard, victoria, alertas, optimizador</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C43" s="16" t="inlineStr">
         <is>
@@ -2201,14 +2197,16 @@
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>4. a) En Marcha Blanca (con pendientes)</t>
+          <t>Detenida</t>
         </is>
       </c>
       <c r="E43" s="17" t="n">
-        <v>350.0</v>
-      </c>
-      <c r="F43" s="17" t="n">
-        <v>40.0</v>
+        <v>500.0</v>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G43" s="16" t="inlineStr">
         <is>
@@ -2217,26 +2215,28 @@
       </c>
       <c r="H43" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I43" s="18" t="n">
-        <v>46289.0</v>
+          <t>Asistencia; Dashboard; Integración Estándar; Módulo Vacaciones</t>
+        </is>
+      </c>
+      <c r="I43" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>PTI-QCS</t>
+          <t>El Papalote</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>Accesos,asistencia, permisos y vacaciones Netafim</t>
+          <t>Implementación - Asistencia - PTIQCS</t>
         </is>
       </c>
       <c r="B44" s="15" t="n">
-        <v>31.39</v>
+        <v>85.71</v>
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
@@ -2245,16 +2245,14 @@
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>3. En Ejecución</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E44" s="17" t="n">
-        <v>230.0</v>
-      </c>
-      <c r="F44" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>350.0</v>
+      </c>
+      <c r="F44" s="17" t="n">
+        <v>40.0</v>
       </c>
       <c r="G44" s="16" t="inlineStr">
         <is>
@@ -2263,41 +2261,39 @@
       </c>
       <c r="H44" s="16" t="inlineStr">
         <is>
-          <t>Acceso; Asistencia; Módulo de permisos; Módulo Vacaciones</t>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I44" s="18" t="n">
-        <v>46272.0</v>
+        <v>46289.0</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>NETAFIM</t>
+          <t>PTI-QCS</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>Accesos Netafim</t>
-        </is>
-      </c>
-      <c r="B45" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Accesos,asistencia, permisos y vacaciones Netafim</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="n">
+        <v>31.39</v>
       </c>
       <c r="C45" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E45" s="17" t="n">
-        <v>155.0</v>
+        <v>230.0</v>
       </c>
       <c r="F45" s="17" t="inlineStr">
         <is>
@@ -2311,13 +2307,11 @@
       </c>
       <c r="H45" s="16" t="inlineStr">
         <is>
-          <t>Acceso</t>
-        </is>
-      </c>
-      <c r="I45" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Acceso; Asistencia; Módulo de permisos; Módulo Vacaciones</t>
+        </is>
+      </c>
+      <c r="I45" s="18" t="n">
+        <v>46272.0</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2389,7 +2383,7 @@
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>3. En Ejecución</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E47" s="17" t="n">
@@ -2422,31 +2416,27 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>IMPLEMENTACION UEEM</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Microsafe, modulo de asistencia</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="n">
+        <v>78.12</v>
       </c>
       <c r="C48" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E48" s="17" t="n">
-        <v>369.0</v>
-      </c>
-      <c r="F48" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>181.0</v>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>182.0</v>
       </c>
       <c r="G48" s="16" t="inlineStr">
         <is>
@@ -2458,25 +2448,23 @@
           <t>Asistencia</t>
         </is>
       </c>
-      <c r="I48" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="I48" s="18" t="n">
+        <v>46258.0</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>Instituto UEEM</t>
+          <t>Microsafe Mx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Microsafe, modulo de asistencia</t>
+          <t>Schätz &amp; Catanni</t>
         </is>
       </c>
       <c r="B49" s="15" t="n">
-        <v>78.12</v>
+        <v>80.43</v>
       </c>
       <c r="C49" s="16" t="inlineStr">
         <is>
@@ -2489,10 +2477,10 @@
         </is>
       </c>
       <c r="E49" s="17" t="n">
-        <v>181.0</v>
+        <v>60.0</v>
       </c>
       <c r="F49" s="17" t="n">
-        <v>182.0</v>
+        <v>50.0</v>
       </c>
       <c r="G49" s="16" t="inlineStr">
         <is>
@@ -2501,46 +2489,42 @@
       </c>
       <c r="H49" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
+          <t>Asistencia; Módulo Vacaciones</t>
         </is>
       </c>
       <c r="I49" s="18" t="n">
-        <v>46237.0</v>
+        <v>46252.0</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>Microsafe Mx</t>
+          <t>Schätz &amp; Cattani Spa México</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Microsafe, modulo de asistencia</t>
-        </is>
-      </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Servicios integrales de logistica NURIB</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="n">
+        <v>0.0</v>
       </c>
       <c r="C50" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E50" s="17" t="n">
-        <v>181.0</v>
-      </c>
-      <c r="F50" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>4.0</v>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>4.0</v>
       </c>
       <c r="G50" s="16" t="inlineStr">
         <is>
@@ -2559,18 +2543,18 @@
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>Microsafe Mx</t>
+          <t>Servicios integrales de logistica NURIB</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Schätz &amp; Catanni</t>
+          <t>Implementación DIVYA</t>
         </is>
       </c>
       <c r="B51" s="15" t="n">
-        <v>80.43</v>
+        <v>2.97</v>
       </c>
       <c r="C51" s="16" t="inlineStr">
         <is>
@@ -2583,10 +2567,10 @@
         </is>
       </c>
       <c r="E51" s="17" t="n">
-        <v>60.0</v>
+        <v>130.0</v>
       </c>
       <c r="F51" s="17" t="n">
-        <v>50.0</v>
+        <v>104.0</v>
       </c>
       <c r="G51" s="16" t="inlineStr">
         <is>
@@ -2599,26 +2583,28 @@
         </is>
       </c>
       <c r="I51" s="18" t="n">
-        <v>46252.0</v>
+        <v>46260.0</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>Schätz &amp; Cattani Spa México</t>
+          <t>DIVYA</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>Servicios integrales de logistica NURIB</t>
-        </is>
-      </c>
-      <c r="B52" s="15" t="n">
-        <v>0.0</v>
+          <t>SIES Implementación</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C52" s="16" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
@@ -2627,10 +2613,12 @@
         </is>
       </c>
       <c r="E52" s="17" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F52" s="17" t="n">
-        <v>4.0</v>
+        <v>220.0</v>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G52" s="16" t="inlineStr">
         <is>
@@ -2639,28 +2627,26 @@
       </c>
       <c r="H52" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I52" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia; Comedor; Módulo Vacaciones</t>
+        </is>
+      </c>
+      <c r="I52" s="18" t="n">
+        <v>46244.0</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>Servicios integrales de logistica NURIB</t>
+          <t>SOCIEDAD INDUSTRIAL EQUIPOS Y SERVICIOS SAPI DE CV</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>Implementación DIVYA</t>
+          <t>PENHEALTH - ASISTENCIA</t>
         </is>
       </c>
       <c r="B53" s="15" t="n">
-        <v>2.97</v>
+        <v>38.08</v>
       </c>
       <c r="C53" s="16" t="inlineStr">
         <is>
@@ -2673,53 +2659,51 @@
         </is>
       </c>
       <c r="E53" s="17" t="n">
-        <v>130.0</v>
+        <v>292.0</v>
       </c>
       <c r="F53" s="17" t="n">
-        <v>104.0</v>
+        <v>292.0</v>
       </c>
       <c r="G53" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Partnea</t>
         </is>
       </c>
       <c r="H53" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I53" s="18" t="n">
-        <v>46260.0</v>
+        <v>46257.0</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>DIVYA</t>
+          <t>PENHEALTH</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>ROALSA CARRIERS SA DE CV</t>
-        </is>
-      </c>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Nueva empresa FIDES</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="n">
+        <v>2.59</v>
       </c>
       <c r="C54" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E54" s="17" t="n">
-        <v>4.0</v>
+        <v>138.0</v>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
@@ -2736,27 +2720,23 @@
           <t>Asistencia</t>
         </is>
       </c>
-      <c r="I54" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="I54" s="18" t="n">
+        <v>46229.0</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>Servicios integrales de logistica NURIB</t>
+          <t>HEINEKEN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>SIES Implementación</t>
-        </is>
-      </c>
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Implementación - Asistencia - HIVICO</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="n">
+        <v>91.74</v>
       </c>
       <c r="C55" s="16" t="inlineStr">
         <is>
@@ -2769,7 +2749,7 @@
         </is>
       </c>
       <c r="E55" s="17" t="n">
-        <v>220.0</v>
+        <v>102.0</v>
       </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
@@ -2783,26 +2763,26 @@
       </c>
       <c r="H55" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Comedor; Módulo Vacaciones</t>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I55" s="18" t="n">
-        <v>46244.0</v>
+        <v>46210.0</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>SOCIEDAD INDUSTRIAL EQUIPOS Y SERVICIOS SAPI DE CV</t>
+          <t>HIDALGO VIGUERAS CONSULTORES</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>PENHEALTH - ASISTENCIA</t>
+          <t>Implementación - Asistencia - WeeCompany</t>
         </is>
       </c>
       <c r="B56" s="15" t="n">
-        <v>38.08</v>
+        <v>91.36</v>
       </c>
       <c r="C56" s="16" t="inlineStr">
         <is>
@@ -2815,38 +2795,38 @@
         </is>
       </c>
       <c r="E56" s="17" t="n">
-        <v>292.0</v>
+        <v>80.0</v>
       </c>
       <c r="F56" s="17" t="n">
-        <v>292.0</v>
+        <v>80.0</v>
       </c>
       <c r="G56" s="16" t="inlineStr">
         <is>
-          <t>Partnea</t>
+          <t/>
         </is>
       </c>
       <c r="H56" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
+          <t>Acceso; Asistencia</t>
         </is>
       </c>
       <c r="I56" s="18" t="n">
-        <v>46257.0</v>
+        <v>46278.0</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>PENHEALTH</t>
+          <t>WeeCompany</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
-          <t>Nueva empresa FIDES</t>
+          <t>MATER</t>
         </is>
       </c>
       <c r="B57" s="15" t="n">
-        <v>2.59</v>
+        <v>0.0</v>
       </c>
       <c r="C57" s="16" t="inlineStr">
         <is>
@@ -2855,16 +2835,14 @@
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>4. a) En Marcha Blanca (con pendientes)</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E57" s="17" t="n">
-        <v>138.0</v>
-      </c>
-      <c r="F57" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>3.0</v>
+      </c>
+      <c r="F57" s="17" t="n">
+        <v>4.0</v>
       </c>
       <c r="G57" s="16" t="inlineStr">
         <is>
@@ -2873,46 +2851,42 @@
       </c>
       <c r="H57" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
+          <t>Asistencia; Módulo Vacaciones</t>
         </is>
       </c>
       <c r="I57" s="18" t="n">
-        <v>46229.0</v>
+        <v>46208.0</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>Mater</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>SIES Implementación</t>
-        </is>
-      </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>SUMA ENLACES PROFESIONALES</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="n">
+        <v>0.0</v>
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Detenida</t>
         </is>
       </c>
       <c r="E58" s="17" t="n">
-        <v>220.0</v>
-      </c>
-      <c r="F58" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>27.0</v>
+      </c>
+      <c r="F58" s="17" t="n">
+        <v>29.0</v>
       </c>
       <c r="G58" s="16" t="inlineStr">
         <is>
@@ -2921,7 +2895,7 @@
       </c>
       <c r="H58" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Comedor; Módulo Vacaciones</t>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I58" s="18" t="inlineStr">
@@ -2931,18 +2905,18 @@
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>SOCIEDAD INDUSTRIAL EQUIPOS Y SERVICIOS SAPI DE CV</t>
+          <t>IT Work</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
         <is>
-          <t>Implementación - Asistencia - HIVICO</t>
+          <t>Implementación J&amp;T EXPRESS R2 CHIHUAHUA</t>
         </is>
       </c>
       <c r="B59" s="15" t="n">
-        <v>91.74</v>
+        <v>72.53</v>
       </c>
       <c r="C59" s="16" t="inlineStr">
         <is>
@@ -2955,12 +2929,10 @@
         </is>
       </c>
       <c r="E59" s="17" t="n">
-        <v>102.0</v>
-      </c>
-      <c r="F59" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>185.0</v>
+      </c>
+      <c r="F59" s="17" t="n">
+        <v>185.0</v>
       </c>
       <c r="G59" s="16" t="inlineStr">
         <is>
@@ -2973,22 +2945,22 @@
         </is>
       </c>
       <c r="I59" s="18" t="n">
-        <v>46210.0</v>
+        <v>46222.0</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>HIDALGO VIGUERAS CONSULTORES</t>
+          <t>J&amp;T EXPRESS</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>Implementación - Asistencia - WeeCompany</t>
+          <t>Implementación J&amp;T EXPRESS CEDIS TLANEPANTLA</t>
         </is>
       </c>
       <c r="B60" s="15" t="n">
-        <v>91.36</v>
+        <v>85.6</v>
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
@@ -3001,10 +2973,10 @@
         </is>
       </c>
       <c r="E60" s="17" t="n">
-        <v>80.0</v>
+        <v>700.0</v>
       </c>
       <c r="F60" s="17" t="n">
-        <v>80.0</v>
+        <v>160.0</v>
       </c>
       <c r="G60" s="16" t="inlineStr">
         <is>
@@ -3013,42 +2985,42 @@
       </c>
       <c r="H60" s="16" t="inlineStr">
         <is>
-          <t>Acceso; Asistencia</t>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I60" s="18" t="n">
-        <v>46278.0</v>
+        <v>46212.0</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>WeeCompany</t>
+          <t>J&amp;T EXPRESS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="14" t="inlineStr">
         <is>
-          <t>Implementación - Asistencia - WeeMedic</t>
+          <t>LETZEL</t>
         </is>
       </c>
       <c r="B61" s="15" t="n">
-        <v>0.37</v>
+        <v>0.0</v>
       </c>
       <c r="C61" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E61" s="17" t="n">
-        <v>270.0</v>
+        <v>10.0</v>
       </c>
       <c r="F61" s="17" t="n">
-        <v>270.0</v>
+        <v>13.0</v>
       </c>
       <c r="G61" s="16" t="inlineStr">
         <is>
@@ -3057,22 +3029,24 @@
       </c>
       <c r="H61" s="16" t="inlineStr">
         <is>
-          <t>Acceso; Asistencia</t>
-        </is>
-      </c>
-      <c r="I61" s="18" t="n">
-        <v>46243.0</v>
+          <t>Asistencia</t>
+        </is>
+      </c>
+      <c r="I61" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>WeeMedic</t>
+          <t>LETZEL S.A DE C.V</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>MATER</t>
+          <t>OVG - Asistencia</t>
         </is>
       </c>
       <c r="B62" s="15" t="n">
@@ -3085,14 +3059,14 @@
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>Abandono</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E62" s="17" t="n">
-        <v>3.0</v>
+        <v>2500.0</v>
       </c>
       <c r="F62" s="17" t="n">
-        <v>4.0</v>
+        <v>2411.0</v>
       </c>
       <c r="G62" s="16" t="inlineStr">
         <is>
@@ -3101,26 +3075,28 @@
       </c>
       <c r="H62" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I62" s="18" t="n">
-        <v>46208.0</v>
+        <v>46226.0</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>Mater</t>
+          <t>OVG</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="14" t="inlineStr">
         <is>
-          <t>Implementación J&amp;T EXPRESS YUCATAN R7</t>
-        </is>
-      </c>
-      <c r="B63" s="15" t="n">
-        <v>91.6</v>
+          <t>ESAI</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C63" s="16" t="inlineStr">
         <is>
@@ -3129,14 +3105,16 @@
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>4. b) En Marcha Blanca (sin pendientes)</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E63" s="17" t="n">
-        <v>150.0</v>
-      </c>
-      <c r="F63" s="17" t="n">
-        <v>115.0</v>
+        <v>20.0</v>
+      </c>
+      <c r="F63" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G63" s="16" t="inlineStr">
         <is>
@@ -3145,22 +3123,24 @@
       </c>
       <c r="H63" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I63" s="18" t="n">
-        <v>46222.0</v>
+          <t>Asistencia; Módulo Vacaciones</t>
+        </is>
+      </c>
+      <c r="I63" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>J&amp;T EXPRESS</t>
+          <t>ESAI</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>SUMA ENLACES PROFESIONALES</t>
+          <t>ROKKINA</t>
         </is>
       </c>
       <c r="B64" s="15" t="n">
@@ -3177,10 +3157,10 @@
         </is>
       </c>
       <c r="E64" s="17" t="n">
-        <v>27.0</v>
+        <v>75.0</v>
       </c>
       <c r="F64" s="17" t="n">
-        <v>29.0</v>
+        <v>76.0</v>
       </c>
       <c r="G64" s="16" t="inlineStr">
         <is>
@@ -3199,38 +3179,38 @@
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>IT Work</t>
+          <t>ROKKINA</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="14" t="inlineStr">
         <is>
-          <t>Implementación J&amp;T EXPRESS R2 CHIHUAHUA</t>
+          <t>WALLGROW - ASISTENCIA</t>
         </is>
       </c>
       <c r="B65" s="15" t="n">
-        <v>71.81</v>
+        <v>1.28</v>
       </c>
       <c r="C65" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>4. a) En Marcha Blanca (con pendientes)</t>
+          <t>Detenida</t>
         </is>
       </c>
       <c r="E65" s="17" t="n">
-        <v>185.0</v>
+        <v>39.0</v>
       </c>
       <c r="F65" s="17" t="n">
-        <v>185.0</v>
+        <v>77.0</v>
       </c>
       <c r="G65" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Julio Cesar Duarte</t>
         </is>
       </c>
       <c r="H65" s="16" t="inlineStr">
@@ -3238,23 +3218,25 @@
           <t>Asistencia</t>
         </is>
       </c>
-      <c r="I65" s="18" t="n">
-        <v>46222.0</v>
+      <c r="I65" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>J&amp;T EXPRESS</t>
+          <t>WALLGROW</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>Implementación J&amp;T EXPRESS CEDIS TLANEPANTLA</t>
+          <t>Schindler - Asistencia - Formularios</t>
         </is>
       </c>
       <c r="B66" s="15" t="n">
-        <v>85.6</v>
+        <v>0.0</v>
       </c>
       <c r="C66" s="16" t="inlineStr">
         <is>
@@ -3263,14 +3245,14 @@
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>4. a) En Marcha Blanca (con pendientes)</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E66" s="17" t="n">
-        <v>700.0</v>
+        <v>20.0</v>
       </c>
       <c r="F66" s="17" t="n">
-        <v>160.0</v>
+        <v>12.0</v>
       </c>
       <c r="G66" s="16" t="inlineStr">
         <is>
@@ -3279,26 +3261,28 @@
       </c>
       <c r="H66" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I66" s="18" t="n">
-        <v>46212.0</v>
+          <t>Asistencia; Personalización</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>J&amp;T EXPRESS</t>
+          <t>SCHINDLER SA DE CV</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="14" t="inlineStr">
         <is>
-          <t>LETZEL</t>
+          <t>HEXAGON MINING SA DE CV</t>
         </is>
       </c>
       <c r="B67" s="15" t="n">
-        <v>0.0</v>
+        <v>10.96</v>
       </c>
       <c r="C67" s="16" t="inlineStr">
         <is>
@@ -3311,10 +3295,10 @@
         </is>
       </c>
       <c r="E67" s="17" t="n">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
       <c r="F67" s="17" t="n">
-        <v>13.0</v>
+        <v>72.0</v>
       </c>
       <c r="G67" s="16" t="inlineStr">
         <is>
@@ -3333,14 +3317,14 @@
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>LETZEL S.A DE C.V</t>
+          <t>HEXAGON MINING SA DE CV</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>OVG - Asistencia</t>
+          <t>TUSSAN</t>
         </is>
       </c>
       <c r="B68" s="15" t="n">
@@ -3348,19 +3332,21 @@
       </c>
       <c r="C68" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>4. a) En Marcha Blanca (con pendientes)</t>
+          <t>Detenida</t>
         </is>
       </c>
       <c r="E68" s="17" t="n">
-        <v>2500.0</v>
-      </c>
-      <c r="F68" s="17" t="n">
-        <v>2411.0</v>
+        <v>13.0</v>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G68" s="16" t="inlineStr">
         <is>
@@ -3372,19 +3358,21 @@
           <t>Asistencia</t>
         </is>
       </c>
-      <c r="I68" s="18" t="n">
-        <v>46226.0</v>
+      <c r="I68" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>OVG</t>
+          <t>TUSSAN</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="14" t="inlineStr">
         <is>
-          <t>Omnilaser Medical</t>
+          <t>Implementación Hermos Asistencia+Vacaciones</t>
         </is>
       </c>
       <c r="B69" s="15" t="inlineStr">
@@ -3394,16 +3382,16 @@
       </c>
       <c r="C69" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>4. b) En Marcha Blanca (sin pendientes)</t>
         </is>
       </c>
       <c r="E69" s="17" t="n">
-        <v>14.0</v>
+        <v>267.0</v>
       </c>
       <c r="F69" s="17" t="inlineStr">
         <is>
@@ -3417,34 +3405,30 @@
       </c>
       <c r="H69" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I69" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia; Módulo Vacaciones</t>
+        </is>
+      </c>
+      <c r="I69" s="18" t="n">
+        <v>46232.0</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>Omnilaser Medical</t>
+          <t>Hermos</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>ESAI</t>
-        </is>
-      </c>
-      <c r="B70" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Comercializadora El Bombon</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="n">
+        <v>0.0</v>
       </c>
       <c r="C70" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
@@ -3453,12 +3437,10 @@
         </is>
       </c>
       <c r="E70" s="17" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F70" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>3.0</v>
+      </c>
+      <c r="F70" s="17" t="n">
+        <v>3.0</v>
       </c>
       <c r="G70" s="16" t="inlineStr">
         <is>
@@ -3467,7 +3449,7 @@
       </c>
       <c r="H70" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I70" s="18" t="inlineStr">
@@ -3477,64 +3459,62 @@
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>ESAI</t>
+          <t>COMERCIALIZADORA EL BOMBON</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="14" t="inlineStr">
         <is>
-          <t>ROKKINA</t>
+          <t>TRANSPORTES RUGA - ASISTENCIA + VACACIONES</t>
         </is>
       </c>
       <c r="B71" s="15" t="n">
-        <v>0.0</v>
+        <v>54.46</v>
       </c>
       <c r="C71" s="16" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>Detenida</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E71" s="17" t="n">
-        <v>75.0</v>
+        <v>610.0</v>
       </c>
       <c r="F71" s="17" t="n">
-        <v>76.0</v>
+        <v>604.0</v>
       </c>
       <c r="G71" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="H71" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I71" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia; Módulo de permisos; Módulo Vacaciones</t>
+        </is>
+      </c>
+      <c r="I71" s="18" t="n">
+        <v>46231.0</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>ROKKINA</t>
+          <t>Transportes Ruga</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>WALLGROW - ASISTENCIA</t>
+          <t>DRILLMEC</t>
         </is>
       </c>
       <c r="B72" s="15" t="n">
-        <v>1.3</v>
+        <v>0.0</v>
       </c>
       <c r="C72" s="16" t="inlineStr">
         <is>
@@ -3547,14 +3527,14 @@
         </is>
       </c>
       <c r="E72" s="17" t="n">
-        <v>39.0</v>
+        <v>24.0</v>
       </c>
       <c r="F72" s="17" t="n">
-        <v>39.0</v>
+        <v>24.0</v>
       </c>
       <c r="G72" s="16" t="inlineStr">
         <is>
-          <t>Julio Cesar Duarte</t>
+          <t/>
         </is>
       </c>
       <c r="H72" s="16" t="inlineStr">
@@ -3569,18 +3549,18 @@
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>WALLGROW</t>
+          <t>DRILLMEC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="14" t="inlineStr">
         <is>
-          <t>Schindler - Asistencia - Formularios</t>
+          <t>Almacenadora AlSur</t>
         </is>
       </c>
       <c r="B73" s="15" t="n">
-        <v>0.0</v>
+        <v>9.22</v>
       </c>
       <c r="C73" s="16" t="inlineStr">
         <is>
@@ -3589,14 +3569,14 @@
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>Abandono</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E73" s="17" t="n">
-        <v>20.0</v>
+        <v>332.0</v>
       </c>
       <c r="F73" s="17" t="n">
-        <v>12.0</v>
+        <v>337.0</v>
       </c>
       <c r="G73" s="16" t="inlineStr">
         <is>
@@ -3605,32 +3585,30 @@
       </c>
       <c r="H73" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Personalización</t>
-        </is>
-      </c>
-      <c r="I73" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia</t>
+        </is>
+      </c>
+      <c r="I73" s="18" t="n">
+        <v>46210.0</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>SCHINDLER SA DE CV</t>
+          <t>Almacenadora Sur SA de CV</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>HEXAGON MINING SA DE CV</t>
+          <t>Implementación J&amp;T EXPRESS JALISCO</t>
         </is>
       </c>
       <c r="B74" s="15" t="n">
-        <v>10.96</v>
+        <v>38.2</v>
       </c>
       <c r="C74" s="16" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
@@ -3639,10 +3617,10 @@
         </is>
       </c>
       <c r="E74" s="17" t="n">
-        <v>100.0</v>
+        <v>248.0</v>
       </c>
       <c r="F74" s="17" t="n">
-        <v>72.0</v>
+        <v>292.0</v>
       </c>
       <c r="G74" s="16" t="inlineStr">
         <is>
@@ -3651,28 +3629,26 @@
       </c>
       <c r="H74" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I74" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia; Módulo Vacaciones</t>
+        </is>
+      </c>
+      <c r="I74" s="18" t="n">
+        <v>46203.0</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
-          <t>HEXAGON MINING SA DE CV</t>
+          <t>J&amp;T EXPRESS</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="14" t="inlineStr">
         <is>
-          <t>TUSSAN</t>
+          <t>MOGAR SEGURIDAD</t>
         </is>
       </c>
       <c r="B75" s="15" t="n">
-        <v>0.0</v>
+        <v>2.78</v>
       </c>
       <c r="C75" s="16" t="inlineStr">
         <is>
@@ -3685,12 +3661,10 @@
         </is>
       </c>
       <c r="E75" s="17" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="F75" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>130.0</v>
+      </c>
+      <c r="F75" s="17" t="n">
+        <v>16.0</v>
       </c>
       <c r="G75" s="16" t="inlineStr">
         <is>
@@ -3709,38 +3683,34 @@
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>TUSSAN</t>
+          <t>Mogar Seguridad Privada</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>TUSSAN</t>
-        </is>
-      </c>
-      <c r="B76" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>IMPLEMENTACION NORVER</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="n">
+        <v>91.43</v>
       </c>
       <c r="C76" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>4. b) En Marcha Blanca (sin pendientes)</t>
         </is>
       </c>
       <c r="E76" s="17" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="F76" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>43.0</v>
+      </c>
+      <c r="F76" s="17" t="n">
+        <v>41.0</v>
       </c>
       <c r="G76" s="16" t="inlineStr">
         <is>
@@ -3749,30 +3719,26 @@
       </c>
       <c r="H76" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I76" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia; Módulo Vacaciones</t>
+        </is>
+      </c>
+      <c r="I76" s="18" t="n">
+        <v>46198.0</v>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>TUSSAN</t>
+          <t>Empacadora NOR-VER</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="14" t="inlineStr">
         <is>
-          <t>Implementación Hermos Asistencia+Vacaciones</t>
-        </is>
-      </c>
-      <c r="B77" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Accesos internos Softys</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="n">
+        <v>65.3</v>
       </c>
       <c r="C77" s="16" t="inlineStr">
         <is>
@@ -3785,7 +3751,7 @@
         </is>
       </c>
       <c r="E77" s="17" t="n">
-        <v>267.0</v>
+        <v>3200.0</v>
       </c>
       <c r="F77" s="17" t="inlineStr">
         <is>
@@ -3799,46 +3765,42 @@
       </c>
       <c r="H77" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
+          <t>Acceso</t>
         </is>
       </c>
       <c r="I77" s="18" t="n">
-        <v>46232.0</v>
+        <v>46205.0</v>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>Hermos</t>
+          <t>Softys México</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>Comercializadora El Bombon</t>
-        </is>
-      </c>
-      <c r="B78" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Comedores Alva - Modulo de Comedor</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="n">
+        <v>0.0</v>
       </c>
       <c r="C78" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Detenida</t>
         </is>
       </c>
       <c r="E78" s="17" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F78" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>272.0</v>
+      </c>
+      <c r="F78" s="17" t="n">
+        <v>400.0</v>
       </c>
       <c r="G78" s="16" t="inlineStr">
         <is>
@@ -3847,24 +3809,22 @@
       </c>
       <c r="H78" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I78" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Comedor</t>
+        </is>
+      </c>
+      <c r="I78" s="18" t="n">
+        <v>46160.0</v>
       </c>
       <c r="J78" s="16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EL BOMBON</t>
+          <t>Comedores alva</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="14" t="inlineStr">
         <is>
-          <t>Comercializadora El Bombon</t>
+          <t>ESAI</t>
         </is>
       </c>
       <c r="B79" s="15" t="n">
@@ -3877,14 +3837,14 @@
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>Detenida</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E79" s="17" t="n">
-        <v>3.0</v>
+        <v>19.0</v>
       </c>
       <c r="F79" s="17" t="n">
-        <v>3.0</v>
+        <v>19.0</v>
       </c>
       <c r="G79" s="16" t="inlineStr">
         <is>
@@ -3903,88 +3863,78 @@
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EL BOMBON</t>
+          <t>ESAI</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>Comercializadora El Bombon</t>
-        </is>
-      </c>
-      <c r="B80" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Implementacion Alliance</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="n">
+        <v>76.4</v>
       </c>
       <c r="C80" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Detenida</t>
         </is>
       </c>
       <c r="E80" s="17" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F80" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>85.0</v>
+      </c>
+      <c r="F80" s="17" t="n">
+        <v>88.0</v>
       </c>
       <c r="G80" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>ERP Solutions</t>
         </is>
       </c>
       <c r="H80" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I80" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia; Módulo Vacaciones</t>
+        </is>
+      </c>
+      <c r="I80" s="18" t="n">
+        <v>46198.0</v>
       </c>
       <c r="J80" s="16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EL BOMBON</t>
+          <t>Alliance Solutions</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="14" t="inlineStr">
         <is>
-          <t>Implementación Finotex</t>
-        </is>
-      </c>
-      <c r="B81" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>URIMAR - Control de comedor</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="n">
+        <v>0.0</v>
       </c>
       <c r="C81" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Detenida</t>
         </is>
       </c>
       <c r="E81" s="17" t="n">
-        <v>160.0</v>
-      </c>
-      <c r="F81" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>1075.0</v>
+      </c>
+      <c r="F81" s="17" t="n">
+        <v>410.0</v>
       </c>
       <c r="G81" s="16" t="inlineStr">
         <is>
@@ -3993,68 +3943,68 @@
       </c>
       <c r="H81" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I81" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Comedor</t>
+        </is>
+      </c>
+      <c r="I81" s="18" t="n">
+        <v>46118.0</v>
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>Finotex</t>
+          <t>Operadora Urimar</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>TRANSPORTES RUGA - ASISTENCIA + VACACIONES</t>
+          <t>Chevewings</t>
         </is>
       </c>
       <c r="B82" s="15" t="n">
-        <v>54.46</v>
+        <v>0.0</v>
       </c>
       <c r="C82" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>4. a) En Marcha Blanca (con pendientes)</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E82" s="17" t="n">
-        <v>610.0</v>
+        <v>106.0</v>
       </c>
       <c r="F82" s="17" t="n">
-        <v>604.0</v>
+        <v>106.0</v>
       </c>
       <c r="G82" s="16" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t/>
         </is>
       </c>
       <c r="H82" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo de permisos; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I82" s="18" t="n">
-        <v>46231.0</v>
+          <t>Asistencia</t>
+        </is>
+      </c>
+      <c r="I82" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J82" s="16" t="inlineStr">
         <is>
-          <t>Transportes Ruga</t>
+          <t>Chevewings</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="14" t="inlineStr">
         <is>
-          <t>DRILLMEC</t>
+          <t>Analisis Ambiental</t>
         </is>
       </c>
       <c r="B83" s="15" t="n">
@@ -4071,14 +4021,14 @@
         </is>
       </c>
       <c r="E83" s="17" t="n">
-        <v>24.0</v>
+        <v>29.0</v>
       </c>
       <c r="F83" s="17" t="n">
-        <v>24.0</v>
+        <v>29.0</v>
       </c>
       <c r="G83" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Partnea</t>
         </is>
       </c>
       <c r="H83" s="16" t="inlineStr">
@@ -4093,38 +4043,38 @@
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>DRILLMEC</t>
+          <t>ANALISIS AMBIENTAL</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>Almacenadora AlSur</t>
+          <t>TASAY CONSTRUCCION</t>
         </is>
       </c>
       <c r="B84" s="15" t="n">
-        <v>9.22</v>
+        <v>0.0</v>
       </c>
       <c r="C84" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>4. a) En Marcha Blanca (con pendientes)</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E84" s="17" t="n">
-        <v>332.0</v>
+        <v>49.0</v>
       </c>
       <c r="F84" s="17" t="n">
-        <v>337.0</v>
+        <v>97.0</v>
       </c>
       <c r="G84" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Jealt</t>
         </is>
       </c>
       <c r="H84" s="16" t="inlineStr">
@@ -4132,23 +4082,25 @@
           <t>Asistencia</t>
         </is>
       </c>
-      <c r="I84" s="18" t="n">
-        <v>46210.0</v>
+      <c r="I84" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J84" s="16" t="inlineStr">
         <is>
-          <t>Almacenadora Sur SA de CV</t>
+          <t>TASAY CONSTRUCCION E INGENIERIA</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="14" t="inlineStr">
         <is>
-          <t>Implementación J&amp;T EXPRESS JALISCO</t>
+          <t>Cuchara y tenedor - Asistencia - Comedor</t>
         </is>
       </c>
       <c r="B85" s="15" t="n">
-        <v>38.2</v>
+        <v>0.0</v>
       </c>
       <c r="C85" s="16" t="inlineStr">
         <is>
@@ -4161,10 +4113,10 @@
         </is>
       </c>
       <c r="E85" s="17" t="n">
-        <v>248.0</v>
+        <v>10.0</v>
       </c>
       <c r="F85" s="17" t="n">
-        <v>292.0</v>
+        <v>584.0</v>
       </c>
       <c r="G85" s="16" t="inlineStr">
         <is>
@@ -4173,42 +4125,42 @@
       </c>
       <c r="H85" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
+          <t>Asistencia; Comedor</t>
         </is>
       </c>
       <c r="I85" s="18" t="n">
-        <v>46203.0</v>
+        <v>46160.0</v>
       </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
-          <t>J&amp;T EXPRESS</t>
+          <t>Cuchara y Tenedor</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>MOGAR SEGURIDAD</t>
+          <t>VI Group - asistencia</t>
         </is>
       </c>
       <c r="B86" s="15" t="n">
-        <v>2.78</v>
+        <v>88.14</v>
       </c>
       <c r="C86" s="16" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>Detenida</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E86" s="17" t="n">
-        <v>130.0</v>
+        <v>300.0</v>
       </c>
       <c r="F86" s="17" t="n">
-        <v>16.0</v>
+        <v>301.0</v>
       </c>
       <c r="G86" s="16" t="inlineStr">
         <is>
@@ -4220,41 +4172,39 @@
           <t>Asistencia</t>
         </is>
       </c>
-      <c r="I86" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="I86" s="18" t="n">
+        <v>46233.0</v>
       </c>
       <c r="J86" s="16" t="inlineStr">
         <is>
-          <t>Mogar Seguridad Privada</t>
+          <t>VI GROUP MX</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="14" t="inlineStr">
         <is>
-          <t>IMPLEMENTACION NORVER</t>
+          <t>TADAIMA TIJUANA</t>
         </is>
       </c>
       <c r="B87" s="15" t="n">
-        <v>88.57</v>
+        <v>0.0</v>
       </c>
       <c r="C87" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>4. b) En Marcha Blanca (sin pendientes)</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E87" s="17" t="n">
-        <v>43.0</v>
+        <v>10.0</v>
       </c>
       <c r="F87" s="17" t="n">
-        <v>41.0</v>
+        <v>10.0</v>
       </c>
       <c r="G87" s="16" t="inlineStr">
         <is>
@@ -4263,22 +4213,24 @@
       </c>
       <c r="H87" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I87" s="18" t="n">
-        <v>46198.0</v>
+          <t>Asistencia</t>
+        </is>
+      </c>
+      <c r="I87" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
-          <t>Empacadora NOR-VER</t>
+          <t>Tadaima Tijuana</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>IMPLEMENTACION NORVER</t>
+          <t>Greennova - Asistencia / Vacaciones - App / Biométrico</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
@@ -4288,16 +4240,16 @@
       </c>
       <c r="C88" s="16" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E88" s="17" t="n">
-        <v>43.0</v>
+        <v>220.0</v>
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
@@ -4321,18 +4273,18 @@
       </c>
       <c r="J88" s="16" t="inlineStr">
         <is>
-          <t>Empacadora NOR-VER</t>
+          <t>GREENNOVA ESPECIALIDADES AGRICOLAS</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="14" t="inlineStr">
         <is>
-          <t>Implementación Modulo de Vacaciones y Permisos</t>
+          <t>CTS - ALTUR - ASISTENCIA - APP</t>
         </is>
       </c>
       <c r="B89" s="15" t="n">
-        <v>0.44</v>
+        <v>97.72</v>
       </c>
       <c r="C89" s="16" t="inlineStr">
         <is>
@@ -4341,14 +4293,14 @@
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E89" s="17" t="n">
-        <v>228.0</v>
+        <v>550.0</v>
       </c>
       <c r="F89" s="17" t="n">
-        <v>228.0</v>
+        <v>548.0</v>
       </c>
       <c r="G89" s="16" t="inlineStr">
         <is>
@@ -4357,48 +4309,42 @@
       </c>
       <c r="H89" s="16" t="inlineStr">
         <is>
-          <t>Módulo de permisos; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I89" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia</t>
+        </is>
+      </c>
+      <c r="I89" s="18" t="n">
+        <v>46203.0</v>
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>J&amp;T EXPRESS</t>
+          <t>CTS /Altour</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>Implementación Modulo de Vacaciones / Permisos</t>
-        </is>
-      </c>
-      <c r="B90" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Implementación - Asistencia - Franquicias COLMEX</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="n">
+        <v>0.0</v>
       </c>
       <c r="C90" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E90" s="17" t="n">
-        <v>228.0</v>
-      </c>
-      <c r="F90" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>12.0</v>
+      </c>
+      <c r="F90" s="17" t="n">
+        <v>14.0</v>
       </c>
       <c r="G90" s="16" t="inlineStr">
         <is>
@@ -4407,7 +4353,7 @@
       </c>
       <c r="H90" s="16" t="inlineStr">
         <is>
-          <t>Módulo de permisos; Módulo Vacaciones</t>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I90" s="18" t="inlineStr">
@@ -4417,38 +4363,34 @@
       </c>
       <c r="J90" s="16" t="inlineStr">
         <is>
-          <t>J&amp;T EXPRESS</t>
+          <t>Franquicias Colmex</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="14" t="inlineStr">
         <is>
-          <t>SAMAMEXPORTS - Asistencia</t>
-        </is>
-      </c>
-      <c r="B91" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Grupo Ramo</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="n">
+        <v>0.0</v>
       </c>
       <c r="C91" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D91" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E91" s="17" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="F91" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>172.0</v>
+      </c>
+      <c r="F91" s="17" t="n">
+        <v>172.0</v>
       </c>
       <c r="G91" s="16" t="inlineStr">
         <is>
@@ -4457,7 +4399,7 @@
       </c>
       <c r="H91" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I91" s="18" t="inlineStr">
@@ -4467,38 +4409,34 @@
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
-          <t>SAMAMEXPORTS</t>
+          <t>Grupo Ramo</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>IMPLEMENTACION NORVER</t>
-        </is>
-      </c>
-      <c r="B92" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>GRUPO PASCAL</t>
+        </is>
+      </c>
+      <c r="B92" s="15" t="n">
+        <v>0.0</v>
       </c>
       <c r="C92" s="16" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Finalizado por no show</t>
         </is>
       </c>
       <c r="E92" s="17" t="n">
-        <v>43.0</v>
-      </c>
-      <c r="F92" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>12.0</v>
+      </c>
+      <c r="F92" s="17" t="n">
+        <v>12.0</v>
       </c>
       <c r="G92" s="16" t="inlineStr">
         <is>
@@ -4510,25 +4448,25 @@
           <t>Asistencia</t>
         </is>
       </c>
-      <c r="I92" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="I92" s="18" t="n">
+        <v>45939.0</v>
       </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
-          <t>Empacadora NOR-VER</t>
+          <t>Grupo Pascal</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="14" t="inlineStr">
         <is>
-          <t>Accesos internos Softys</t>
-        </is>
-      </c>
-      <c r="B93" s="15" t="n">
-        <v>66.96</v>
+          <t>Implementación de asistencia DHL Transportes (Corporativo)</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C93" s="16" t="inlineStr">
         <is>
@@ -4541,7 +4479,7 @@
         </is>
       </c>
       <c r="E93" s="17" t="n">
-        <v>3200.0</v>
+        <v>438.0</v>
       </c>
       <c r="F93" s="17" t="inlineStr">
         <is>
@@ -4555,46 +4493,42 @@
       </c>
       <c r="H93" s="16" t="inlineStr">
         <is>
-          <t>Acceso</t>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I93" s="18" t="n">
-        <v>46205.0</v>
+        <v>46121.0</v>
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>Softys México</t>
+          <t>DHL Transportes</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>IMPLEMENTACION NORVER</t>
-        </is>
-      </c>
-      <c r="B94" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Newrest - Asistencia</t>
+        </is>
+      </c>
+      <c r="B94" s="15" t="n">
+        <v>85.57</v>
       </c>
       <c r="C94" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E94" s="17" t="n">
-        <v>43.0</v>
-      </c>
-      <c r="F94" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>1870.0</v>
+      </c>
+      <c r="F94" s="17" t="n">
+        <v>2244.0</v>
       </c>
       <c r="G94" s="16" t="inlineStr">
         <is>
@@ -4606,41 +4540,39 @@
           <t>Asistencia</t>
         </is>
       </c>
-      <c r="I94" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="I94" s="18" t="n">
+        <v>46184.0</v>
       </c>
       <c r="J94" s="16" t="inlineStr">
         <is>
-          <t>Empacadora NOR-VER</t>
+          <t>Newrest - México</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="14" t="inlineStr">
         <is>
-          <t>Comedores Alva - Modulo de Comedor</t>
+          <t>Miele</t>
         </is>
       </c>
       <c r="B95" s="15" t="n">
-        <v>0.0</v>
+        <v>65.52</v>
       </c>
       <c r="C95" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
         <is>
-          <t>Detenida</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E95" s="17" t="n">
-        <v>272.0</v>
+        <v>26.0</v>
       </c>
       <c r="F95" s="17" t="n">
-        <v>400.0</v>
+        <v>30.0</v>
       </c>
       <c r="G95" s="16" t="inlineStr">
         <is>
@@ -4649,26 +4581,28 @@
       </c>
       <c r="H95" s="16" t="inlineStr">
         <is>
-          <t>Comedor</t>
-        </is>
-      </c>
-      <c r="I95" s="18" t="n">
-        <v>46160.0</v>
+          <t/>
+        </is>
+      </c>
+      <c r="I95" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>Comedores alva</t>
+          <t>Miele</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>ESAI</t>
+          <t>AGUA SAN MARTÍN</t>
         </is>
       </c>
       <c r="B96" s="15" t="n">
-        <v>0.0</v>
+        <v>50.0</v>
       </c>
       <c r="C96" s="16" t="inlineStr">
         <is>
@@ -4677,14 +4611,14 @@
       </c>
       <c r="D96" s="16" t="inlineStr">
         <is>
-          <t>Abandono</t>
+          <t>Finalizado por no show</t>
         </is>
       </c>
       <c r="E96" s="17" t="n">
-        <v>19.0</v>
+        <v>12.0</v>
       </c>
       <c r="F96" s="17" t="n">
-        <v>19.0</v>
+        <v>11.0</v>
       </c>
       <c r="G96" s="16" t="inlineStr">
         <is>
@@ -4693,7 +4627,7 @@
       </c>
       <c r="H96" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
+          <t/>
         </is>
       </c>
       <c r="I96" s="18" t="inlineStr">
@@ -4703,82 +4637,80 @@
       </c>
       <c r="J96" s="16" t="inlineStr">
         <is>
-          <t>ESAI</t>
+          <t>Agua purificadora los volcanes</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="14" t="inlineStr">
         <is>
-          <t>Implementacion Alliance</t>
+          <t>dental art</t>
         </is>
       </c>
       <c r="B97" s="15" t="n">
-        <v>76.4</v>
+        <v>0.0</v>
       </c>
       <c r="C97" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D97" s="16" t="inlineStr">
         <is>
-          <t>Detenida</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E97" s="17" t="n">
-        <v>85.0</v>
+        <v>5.0</v>
       </c>
       <c r="F97" s="17" t="n">
-        <v>88.0</v>
+        <v>5.0</v>
       </c>
       <c r="G97" s="16" t="inlineStr">
         <is>
-          <t>ERP Solutions</t>
+          <t/>
         </is>
       </c>
       <c r="H97" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I97" s="18" t="n">
-        <v>46198.0</v>
+          <t/>
+        </is>
+      </c>
+      <c r="I97" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>Alliance Solutions</t>
+          <t>dental Art</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>Implementación Modulo de Vacaciones y Permisos</t>
-        </is>
-      </c>
-      <c r="B98" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia - E3 consultores - Biometricos</t>
+        </is>
+      </c>
+      <c r="B98" s="15" t="n">
+        <v>0.0</v>
       </c>
       <c r="C98" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D98" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E98" s="17" t="n">
-        <v>90.0</v>
-      </c>
-      <c r="F98" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>326.0</v>
+      </c>
+      <c r="F98" s="17" t="n">
+        <v>403.0</v>
       </c>
       <c r="G98" s="16" t="inlineStr">
         <is>
@@ -4787,24 +4719,22 @@
       </c>
       <c r="H98" s="16" t="inlineStr">
         <is>
-          <t>Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I98" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t/>
+        </is>
+      </c>
+      <c r="I98" s="18" t="n">
+        <v>45960.0</v>
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
-          <t>Transportes Zapata Mejía</t>
+          <t>E3 consultores</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="14" t="inlineStr">
         <is>
-          <t>URIMAR - Control de comedor</t>
+          <t>EQUIPOS Y ACCESORIOS PARA GAS L.P. Y NATURAL</t>
         </is>
       </c>
       <c r="B99" s="15" t="n">
@@ -4812,19 +4742,19 @@
       </c>
       <c r="C99" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D99" s="16" t="inlineStr">
         <is>
-          <t>Detenida</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E99" s="17" t="n">
-        <v>1075.0</v>
+        <v>11.0</v>
       </c>
       <c r="F99" s="17" t="n">
-        <v>410.0</v>
+        <v>11.0</v>
       </c>
       <c r="G99" s="16" t="inlineStr">
         <is>
@@ -4833,46 +4763,44 @@
       </c>
       <c r="H99" s="16" t="inlineStr">
         <is>
-          <t>Comedor</t>
-        </is>
-      </c>
-      <c r="I99" s="18" t="n">
-        <v>46118.0</v>
+          <t/>
+        </is>
+      </c>
+      <c r="I99" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
-          <t>Operadora Urimar</t>
+          <t>Equipos y Accesorios para Gas L.P. y Natural</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>Implementación Hermos Asistencia-Vacaciones</t>
-        </is>
-      </c>
-      <c r="B100" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Implementación - Asistencia - Grupo Horizon</t>
+        </is>
+      </c>
+      <c r="B100" s="15" t="n">
+        <v>78.64</v>
       </c>
       <c r="C100" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D100" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>4. a) En Marcha Blanca (con pendientes)</t>
         </is>
       </c>
       <c r="E100" s="17" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F100" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>615.0</v>
+      </c>
+      <c r="F100" s="17" t="n">
+        <v>331.0</v>
       </c>
       <c r="G100" s="16" t="inlineStr">
         <is>
@@ -4881,24 +4809,22 @@
       </c>
       <c r="H100" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I100" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia</t>
+        </is>
+      </c>
+      <c r="I100" s="18" t="n">
+        <v>46075.0</v>
       </c>
       <c r="J100" s="16" t="inlineStr">
         <is>
-          <t>Hermos</t>
+          <t>HORIZON AUTO LOGISTICS</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="14" t="inlineStr">
         <is>
-          <t>FISIOTERAPIA CONTIGHO</t>
+          <t>DYA Manufacturas - Asistencia reloj biométrico</t>
         </is>
       </c>
       <c r="B101" s="15" t="inlineStr">
@@ -4908,21 +4834,19 @@
       </c>
       <c r="C101" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D101" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E101" s="17" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F101" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>326.0</v>
+      </c>
+      <c r="F101" s="17" t="n">
+        <v>377.0</v>
       </c>
       <c r="G101" s="16" t="inlineStr">
         <is>
@@ -4934,25 +4858,23 @@
           <t>Asistencia</t>
         </is>
       </c>
-      <c r="I101" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="I101" s="18" t="n">
+        <v>45946.0</v>
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>GALI CENTRO DE FISOTERAPIA INTEGRAL S DE RL DE CV</t>
+          <t>DYA MANUFACTURA</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>Chevewings</t>
+          <t>BROTHERS BEEF</t>
         </is>
       </c>
       <c r="B102" s="15" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="C102" s="16" t="inlineStr">
         <is>
@@ -4965,10 +4887,10 @@
         </is>
       </c>
       <c r="E102" s="17" t="n">
-        <v>106.0</v>
+        <v>24.0</v>
       </c>
       <c r="F102" s="17" t="n">
-        <v>106.0</v>
+        <v>24.0</v>
       </c>
       <c r="G102" s="16" t="inlineStr">
         <is>
@@ -4977,7 +4899,7 @@
       </c>
       <c r="H102" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
+          <t/>
         </is>
       </c>
       <c r="I102" s="18" t="inlineStr">
@@ -4987,38 +4909,34 @@
       </c>
       <c r="J102" s="16" t="inlineStr">
         <is>
-          <t>Chevewings</t>
+          <t>BROTHERS BEEF</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="14" t="inlineStr">
         <is>
-          <t>Implementación Asistencia Jalisco</t>
-        </is>
-      </c>
-      <c r="B103" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>MANGO AUDIO</t>
+        </is>
+      </c>
+      <c r="B103" s="15" t="n">
+        <v>0.0</v>
       </c>
       <c r="C103" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D103" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>6. Finalizada sin capacitación</t>
         </is>
       </c>
       <c r="E103" s="17" t="n">
-        <v>260.0</v>
-      </c>
-      <c r="F103" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>9.0</v>
+      </c>
+      <c r="F103" s="17" t="n">
+        <v>9.0</v>
       </c>
       <c r="G103" s="16" t="inlineStr">
         <is>
@@ -5027,7 +4945,7 @@
       </c>
       <c r="H103" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
+          <t/>
         </is>
       </c>
       <c r="I103" s="18" t="inlineStr">
@@ -5037,14 +4955,14 @@
       </c>
       <c r="J103" s="16" t="inlineStr">
         <is>
-          <t>J&amp;T EXPRESS</t>
+          <t>MANGO AUDIO</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>Analisis Ambiental</t>
+          <t>INGENIERÍA GRUPO EMPRESARIAL ACTUAL</t>
         </is>
       </c>
       <c r="B104" s="15" t="n">
@@ -5057,23 +4975,23 @@
       </c>
       <c r="D104" s="16" t="inlineStr">
         <is>
-          <t>Detenida</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E104" s="17" t="n">
-        <v>29.0</v>
+        <v>7.0</v>
       </c>
       <c r="F104" s="17" t="n">
-        <v>29.0</v>
+        <v>7.0</v>
       </c>
       <c r="G104" s="16" t="inlineStr">
         <is>
-          <t>Partnea</t>
+          <t/>
         </is>
       </c>
       <c r="H104" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
+          <t/>
         </is>
       </c>
       <c r="I104" s="18" t="inlineStr">
@@ -5083,38 +5001,34 @@
       </c>
       <c r="J104" s="16" t="inlineStr">
         <is>
-          <t>ANALISIS AMBIENTAL</t>
+          <t>Ingeniería Grupo Empresarial Actual</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="14" t="inlineStr">
         <is>
-          <t>Implementación J&amp;T EXPRESS JALISCO</t>
-        </is>
-      </c>
-      <c r="B105" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>IMPLEMENTACION METRO ASFALTOS</t>
+        </is>
+      </c>
+      <c r="B105" s="15" t="n">
+        <v>51.76</v>
       </c>
       <c r="C105" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D105" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Finalizado por no show</t>
         </is>
       </c>
       <c r="E105" s="17" t="n">
-        <v>260.0</v>
-      </c>
-      <c r="F105" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>93.0</v>
+      </c>
+      <c r="F105" s="17" t="n">
+        <v>93.0</v>
       </c>
       <c r="G105" s="16" t="inlineStr">
         <is>
@@ -5123,7 +5037,7 @@
       </c>
       <c r="H105" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
+          <t/>
         </is>
       </c>
       <c r="I105" s="18" t="inlineStr">
@@ -5133,38 +5047,34 @@
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
-          <t>J&amp;T EXPRESS</t>
+          <t>METRO ASFALTOS</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>Implementación Vacaciones PERI</t>
-        </is>
-      </c>
-      <c r="B106" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Hogan Lovells</t>
+        </is>
+      </c>
+      <c r="B106" s="15" t="n">
+        <v>0.0</v>
       </c>
       <c r="C106" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D106" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E106" s="17" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="F106" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>200.0</v>
+      </c>
+      <c r="F106" s="17" t="n">
+        <v>208.0</v>
       </c>
       <c r="G106" s="16" t="inlineStr">
         <is>
@@ -5173,24 +5083,22 @@
       </c>
       <c r="H106" s="16" t="inlineStr">
         <is>
-          <t>Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I106" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t/>
+        </is>
+      </c>
+      <c r="I106" s="18" t="n">
+        <v>45868.0</v>
       </c>
       <c r="J106" s="16" t="inlineStr">
         <is>
-          <t>PERI Cimbras y Andamios</t>
+          <t>Hogan Lovells</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="14" t="inlineStr">
         <is>
-          <t>TASAY CONSTRUCCION</t>
+          <t>FUNDADORES BEACH CLUB AC</t>
         </is>
       </c>
       <c r="B107" s="15" t="n">
@@ -5203,23 +5111,23 @@
       </c>
       <c r="D107" s="16" t="inlineStr">
         <is>
-          <t>Detenida</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E107" s="17" t="n">
-        <v>49.0</v>
+        <v>19.0</v>
       </c>
       <c r="F107" s="17" t="n">
-        <v>97.0</v>
+        <v>22.0</v>
       </c>
       <c r="G107" s="16" t="inlineStr">
         <is>
-          <t>Jealt</t>
+          <t/>
         </is>
       </c>
       <c r="H107" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
+          <t/>
         </is>
       </c>
       <c r="I107" s="18" t="inlineStr">
@@ -5229,36 +5137,34 @@
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>TASAY CONSTRUCCION E INGENIERIA</t>
+          <t>Fundadores</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>SERVICIOS EMPRESARIALES DE ALTURA</t>
-        </is>
-      </c>
-      <c r="B108" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Control de Asistencia</t>
+        </is>
+      </c>
+      <c r="B108" s="15" t="n">
+        <v>77.92</v>
       </c>
       <c r="C108" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Full</t>
         </is>
       </c>
       <c r="D108" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Detenida</t>
         </is>
       </c>
       <c r="E108" s="17" t="n">
-        <v>13.0</v>
+        <v>622.0</v>
       </c>
       <c r="F108" s="17" t="n">
-        <v>15.0</v>
+        <v>643.0</v>
       </c>
       <c r="G108" s="16" t="inlineStr">
         <is>
@@ -5267,24 +5173,22 @@
       </c>
       <c r="H108" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I108" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t/>
+        </is>
+      </c>
+      <c r="I108" s="18" t="n">
+        <v>45946.0</v>
       </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
-          <t>SERVICIOS EMPRESARIALES DE ALTURA</t>
+          <t>Los Cinco Soles</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="14" t="inlineStr">
         <is>
-          <t>Cuchara y tenedor - Asistencia - Comedor</t>
+          <t>Pensiones Libertad</t>
         </is>
       </c>
       <c r="B109" s="15" t="n">
@@ -5292,19 +5196,19 @@
       </c>
       <c r="C109" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D109" s="16" t="inlineStr">
         <is>
-          <t>Detenida</t>
+          <t>Finalizado por no show</t>
         </is>
       </c>
       <c r="E109" s="17" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="F109" s="17" t="n">
-        <v>584.0</v>
+        <v>8.0</v>
       </c>
       <c r="G109" s="16" t="inlineStr">
         <is>
@@ -5313,55 +5217,53 @@
       </c>
       <c r="H109" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Comedor</t>
-        </is>
-      </c>
-      <c r="I109" s="18" t="n">
-        <v>46160.0</v>
+          <t/>
+        </is>
+      </c>
+      <c r="I109" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>Cuchara y Tenedor</t>
+          <t>Pensiones libertad</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>Implementación DICKA2</t>
-        </is>
-      </c>
-      <c r="B110" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>FREEDOMPOP</t>
+        </is>
+      </c>
+      <c r="B110" s="15" t="n">
+        <v>0.0</v>
       </c>
       <c r="C110" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D110" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E110" s="17" t="n">
-        <v>1200.0</v>
-      </c>
-      <c r="F110" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>39.0</v>
+      </c>
+      <c r="F110" s="17" t="n">
+        <v>41.0</v>
       </c>
       <c r="G110" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Buk</t>
         </is>
       </c>
       <c r="H110" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Dashboard</t>
+          <t/>
         </is>
       </c>
       <c r="I110" s="18" t="inlineStr">
@@ -5371,34 +5273,34 @@
       </c>
       <c r="J110" s="16" t="inlineStr">
         <is>
-          <t>DICKA LOGISTICS</t>
+          <t>FREEDOMPOP MEXICO SA</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="14" t="inlineStr">
         <is>
-          <t>VI Group - asistencia</t>
+          <t>MAFERSA - ASISTENCIA</t>
         </is>
       </c>
       <c r="B111" s="15" t="n">
-        <v>86.39</v>
+        <v>36.61</v>
       </c>
       <c r="C111" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D111" s="16" t="inlineStr">
         <is>
-          <t>4. a) En Marcha Blanca (con pendientes)</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E111" s="17" t="n">
-        <v>300.0</v>
+        <v>126.0</v>
       </c>
       <c r="F111" s="17" t="n">
-        <v>301.0</v>
+        <v>122.0</v>
       </c>
       <c r="G111" s="16" t="inlineStr">
         <is>
@@ -5410,19 +5312,21 @@
           <t>Asistencia</t>
         </is>
       </c>
-      <c r="I111" s="18" t="n">
-        <v>46233.0</v>
+      <c r="I111" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
-          <t>VI GROUP MX</t>
+          <t>Desarrollos MAFERSA</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>TADAIMA TIJUANA</t>
+          <t>ALBERCAS VENZAR</t>
         </is>
       </c>
       <c r="B112" s="15" t="n">
@@ -5439,10 +5343,10 @@
         </is>
       </c>
       <c r="E112" s="17" t="n">
-        <v>10.0</v>
+        <v>53.0</v>
       </c>
       <c r="F112" s="17" t="n">
-        <v>10.0</v>
+        <v>65.0</v>
       </c>
       <c r="G112" s="16" t="inlineStr">
         <is>
@@ -5461,14 +5365,14 @@
       </c>
       <c r="J112" s="16" t="inlineStr">
         <is>
-          <t>Tadaima Tijuana</t>
+          <t>Albercas Venzarr</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="14" t="inlineStr">
         <is>
-          <t>Implementación DICKA</t>
+          <t>NAYARTA ENTERTAIMENT ASISTENCIA</t>
         </is>
       </c>
       <c r="B113" s="15" t="inlineStr">
@@ -5478,21 +5382,19 @@
       </c>
       <c r="C113" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D113" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Finalizado sin uso de plataforma</t>
         </is>
       </c>
       <c r="E113" s="17" t="n">
-        <v>1200.0</v>
-      </c>
-      <c r="F113" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>5.0</v>
+      </c>
+      <c r="F113" s="17" t="n">
+        <v>5.0</v>
       </c>
       <c r="G113" s="16" t="inlineStr">
         <is>
@@ -5501,46 +5403,42 @@
       </c>
       <c r="H113" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Dashboard</t>
-        </is>
-      </c>
-      <c r="I113" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia</t>
+        </is>
+      </c>
+      <c r="I113" s="18" t="n">
+        <v>45827.0</v>
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>DICKA LOGISTICS</t>
+          <t>NAYARTA ENTERTAINMENT</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>Contratistas Softys García</t>
+          <t>GRUPO EMPRESARIAL LA PIRAMIDE</t>
         </is>
       </c>
       <c r="B114" s="15" t="n">
-        <v>70.35</v>
+        <v>100.0</v>
       </c>
       <c r="C114" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D114" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E114" s="17" t="n">
-        <v>700.0</v>
-      </c>
-      <c r="F114" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>163.0</v>
+      </c>
+      <c r="F114" s="17" t="n">
+        <v>6.0</v>
       </c>
       <c r="G114" s="16" t="inlineStr">
         <is>
@@ -5549,7 +5447,7 @@
       </c>
       <c r="H114" s="16" t="inlineStr">
         <is>
-          <t>Acceso</t>
+          <t/>
         </is>
       </c>
       <c r="I114" s="18" t="inlineStr">
@@ -5559,14 +5457,14 @@
       </c>
       <c r="J114" s="16" t="inlineStr">
         <is>
-          <t>Softys México</t>
+          <t>Grupo empresarial la piramide</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="14" t="inlineStr">
         <is>
-          <t>Greennova - Asistencia / Vacaciones - App / Biométrico</t>
+          <t>Módulo de Vacaciones</t>
         </is>
       </c>
       <c r="B115" s="15" t="inlineStr">
@@ -5576,7 +5474,7 @@
       </c>
       <c r="C115" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D115" s="16" t="inlineStr">
@@ -5585,7 +5483,7 @@
         </is>
       </c>
       <c r="E115" s="17" t="n">
-        <v>220.0</v>
+        <v>100.0</v>
       </c>
       <c r="F115" s="17" t="inlineStr">
         <is>
@@ -5599,44 +5497,46 @@
       </c>
       <c r="H115" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I115" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Módulo Vacaciones</t>
+        </is>
+      </c>
+      <c r="I115" s="18" t="n">
+        <v>45743.0</v>
       </c>
       <c r="J115" s="16" t="inlineStr">
         <is>
-          <t>GREENNOVA ESPECIALIDADES AGRICOLAS</t>
+          <t>Transmal</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>CTS - ALTUR - ASISTENCIA - APP</t>
-        </is>
-      </c>
-      <c r="B116" s="15" t="n">
-        <v>95.64</v>
+          <t>Reimplementación Vanity</t>
+        </is>
+      </c>
+      <c r="B116" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C116" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
-          <t>4. a) En Marcha Blanca (con pendientes)</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E116" s="17" t="n">
-        <v>550.0</v>
-      </c>
-      <c r="F116" s="17" t="n">
-        <v>548.0</v>
+        <v>500.0</v>
+      </c>
+      <c r="F116" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G116" s="16" t="inlineStr">
         <is>
@@ -5649,22 +5549,24 @@
         </is>
       </c>
       <c r="I116" s="18" t="n">
-        <v>46203.0</v>
+        <v>45701.0</v>
       </c>
       <c r="J116" s="16" t="inlineStr">
         <is>
-          <t>CTS /Altour</t>
+          <t>Vanity</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="14" t="inlineStr">
         <is>
-          <t>Implementación - Asistencia - Franquicias COLMEX</t>
-        </is>
-      </c>
-      <c r="B117" s="15" t="n">
-        <v>0.0</v>
+          <t>MKP Agrícola</t>
+        </is>
+      </c>
+      <c r="B117" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C117" s="16" t="inlineStr">
         <is>
@@ -5673,14 +5575,16 @@
       </c>
       <c r="D117" s="16" t="inlineStr">
         <is>
-          <t>Detenida</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E117" s="17" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="F117" s="17" t="n">
-        <v>14.0</v>
+        <v>47.0</v>
+      </c>
+      <c r="F117" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G117" s="16" t="inlineStr">
         <is>
@@ -5699,14 +5603,14 @@
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>Franquicias Colmex</t>
+          <t>MKP Agricola MX</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>Accesos TDSYSTEM</t>
+          <t>VEDAT DE MEXICO SA DE CV (asistencia)</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
@@ -5716,16 +5620,16 @@
       </c>
       <c r="C118" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D118" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E118" s="17" t="n">
-        <v>50.0</v>
+        <v>53.0</v>
       </c>
       <c r="F118" s="17" t="inlineStr">
         <is>
@@ -5739,7 +5643,7 @@
       </c>
       <c r="H118" s="16" t="inlineStr">
         <is>
-          <t>Acceso</t>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I118" s="18" t="inlineStr">
@@ -5749,14 +5653,14 @@
       </c>
       <c r="J118" s="16" t="inlineStr">
         <is>
-          <t>Grupo Empresarial TDS</t>
+          <t>VEDAT DE MEXICO SA de CV</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="14" t="inlineStr">
         <is>
-          <t>Dashboard BI y marcaje WA Heineken</t>
+          <t>TOUS</t>
         </is>
       </c>
       <c r="B119" s="15" t="inlineStr">
@@ -5766,16 +5670,16 @@
       </c>
       <c r="C119" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D119" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E119" s="17" t="n">
-        <v>300.0</v>
+        <v>560.0</v>
       </c>
       <c r="F119" s="17" t="inlineStr">
         <is>
@@ -5789,7 +5693,7 @@
       </c>
       <c r="H119" s="16" t="inlineStr">
         <is>
-          <t>Asistencia; Dashboard</t>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I119" s="18" t="inlineStr">
@@ -5799,18 +5703,20 @@
       </c>
       <c r="J119" s="16" t="inlineStr">
         <is>
-          <t>HEINEKEN</t>
+          <t>TOUS</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>Grupo Ramo</t>
-        </is>
-      </c>
-      <c r="B120" s="15" t="n">
-        <v>0.0</v>
+          <t>Puebla Agricola - Control de asistencia</t>
+        </is>
+      </c>
+      <c r="B120" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C120" s="16" t="inlineStr">
         <is>
@@ -5823,10 +5729,12 @@
         </is>
       </c>
       <c r="E120" s="17" t="n">
-        <v>172.0</v>
-      </c>
-      <c r="F120" s="17" t="n">
-        <v>172.0</v>
+        <v>7.0</v>
+      </c>
+      <c r="F120" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G120" s="16" t="inlineStr">
         <is>
@@ -5845,34 +5753,38 @@
       </c>
       <c r="J120" s="16" t="inlineStr">
         <is>
-          <t>Grupo Ramo</t>
+          <t>Puebla Agrícola</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="14" t="inlineStr">
         <is>
-          <t>GRUPO PASCAL</t>
-        </is>
-      </c>
-      <c r="B121" s="15" t="n">
-        <v>0.0</v>
+          <t>Modulo Vacaciones - Grupo REM</t>
+        </is>
+      </c>
+      <c r="B121" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C121" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D121" s="16" t="inlineStr">
         <is>
-          <t>Finalizado por no show</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E121" s="17" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="F121" s="17" t="n">
-        <v>12.0</v>
+        <v>170.0</v>
+      </c>
+      <c r="F121" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G121" s="16" t="inlineStr">
         <is>
@@ -5881,22 +5793,24 @@
       </c>
       <c r="H121" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I121" s="18" t="n">
-        <v>45939.0</v>
+          <t>Módulo Vacaciones</t>
+        </is>
+      </c>
+      <c r="I121" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
-          <t>Grupo Pascal</t>
+          <t>COMEX MEXICALI</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>Implementación de asistencia DHL Transportes (Corporativo)</t>
+          <t>Implementación Control de Asistencia Laboratorio SantaMaria</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
@@ -5906,16 +5820,16 @@
       </c>
       <c r="C122" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D122" s="16" t="inlineStr">
         <is>
-          <t>4. b) En Marcha Blanca (sin pendientes)</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E122" s="17" t="n">
-        <v>438.0</v>
+        <v>560.0</v>
       </c>
       <c r="F122" s="17" t="inlineStr">
         <is>
@@ -5933,38 +5847,42 @@
         </is>
       </c>
       <c r="I122" s="18" t="n">
-        <v>46121.0</v>
+        <v>45680.0</v>
       </c>
       <c r="J122" s="16" t="inlineStr">
         <is>
-          <t>DHL Transportes</t>
+          <t>Laboratorio Santamaría</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="14" t="inlineStr">
         <is>
-          <t>Newrest - Asistencia</t>
-        </is>
-      </c>
-      <c r="B123" s="15" t="n">
-        <v>85.18</v>
+          <t>Marel México</t>
+        </is>
+      </c>
+      <c r="B123" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C123" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D123" s="16" t="inlineStr">
         <is>
-          <t>4. a) En Marcha Blanca (con pendientes)</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E123" s="17" t="n">
-        <v>1870.0</v>
-      </c>
-      <c r="F123" s="17" t="n">
-        <v>2244.0</v>
+        <v>19.0</v>
+      </c>
+      <c r="F123" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G123" s="16" t="inlineStr">
         <is>
@@ -5973,22 +5891,22 @@
       </c>
       <c r="H123" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
+          <t>Formas de Pago</t>
         </is>
       </c>
       <c r="I123" s="18" t="n">
-        <v>46184.0</v>
+        <v>45715.0</v>
       </c>
       <c r="J123" s="16" t="inlineStr">
         <is>
-          <t>Newrest - México</t>
+          <t>MAREL MEXICO</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>oftalmologos San Angel</t>
+          <t>DDVC</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
@@ -5998,16 +5916,16 @@
       </c>
       <c r="C124" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D124" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E124" s="17" t="n">
-        <v>24.0</v>
+        <v>305.0</v>
       </c>
       <c r="F124" s="17" t="inlineStr">
         <is>
@@ -6024,41 +5942,41 @@
           <t>Asistencia</t>
         </is>
       </c>
-      <c r="I124" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="I124" s="18" t="n">
+        <v>45573.0</v>
       </c>
       <c r="J124" s="16" t="inlineStr">
         <is>
-          <t>San Angel oftalmología México</t>
+          <t>DEPOSITO DENTAL VILLA DE CORTES</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="14" t="inlineStr">
         <is>
-          <t>Bioinsumos Agricolas de Jalisco</t>
-        </is>
-      </c>
-      <c r="B125" s="15" t="n">
-        <v>0.0</v>
+          <t>Universidad Tecnológica de Querétaro</t>
+        </is>
+      </c>
+      <c r="B125" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C125" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D125" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E125" s="17" t="n">
-        <v>11.0</v>
+        <v>561.0</v>
       </c>
       <c r="F125" s="17" t="n">
-        <v>12.0</v>
+        <v>512.0</v>
       </c>
       <c r="G125" s="16" t="inlineStr">
         <is>
@@ -6067,24 +5985,22 @@
       </c>
       <c r="H125" s="16" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I125" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Asistencia</t>
+        </is>
+      </c>
+      <c r="I125" s="18" t="n">
+        <v>45722.0</v>
       </c>
       <c r="J125" s="16" t="inlineStr">
         <is>
-          <t>Bioinsumos Agricolas de Jalisco</t>
+          <t>UTEQ</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>Implementación Modulo de Vacaciones y BI SGS</t>
+          <t>PAN AMERICAN SILVER</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
@@ -6094,16 +6010,16 @@
       </c>
       <c r="C126" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D126" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E126" s="17" t="n">
-        <v>619.0</v>
+        <v>1185.0</v>
       </c>
       <c r="F126" s="17" t="inlineStr">
         <is>
@@ -6117,28 +6033,28 @@
       </c>
       <c r="H126" s="16" t="inlineStr">
         <is>
-          <t>Dashboard; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I126" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+          <t>Comedor</t>
+        </is>
+      </c>
+      <c r="I126" s="18" t="n">
+        <v>45564.0</v>
       </c>
       <c r="J126" s="16" t="inlineStr">
         <is>
-          <t>SGS MEXICO</t>
+          <t>PAN AMERICAN SILVER</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="14" t="inlineStr">
         <is>
-          <t>Miele</t>
-        </is>
-      </c>
-      <c r="B127" s="15" t="n">
-        <v>65.52</v>
+          <t>ANTROMEX</t>
+        </is>
+      </c>
+      <c r="B127" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C127" s="16" t="inlineStr">
         <is>
@@ -6151,10 +6067,12 @@
         </is>
       </c>
       <c r="E127" s="17" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="F127" s="17" t="n">
-        <v>30.0</v>
+        <v>136.0</v>
+      </c>
+      <c r="F127" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G127" s="16" t="inlineStr">
         <is>
@@ -6163,7 +6081,7 @@
       </c>
       <c r="H127" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I127" s="18" t="inlineStr">
@@ -6173,18 +6091,20 @@
       </c>
       <c r="J127" s="16" t="inlineStr">
         <is>
-          <t>Miele</t>
+          <t>ANTROMEX</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>AGUA SAN MARTÍN</t>
-        </is>
-      </c>
-      <c r="B128" s="15" t="n">
-        <v>50.0</v>
+          <t>99 MINUTOS MX</t>
+        </is>
+      </c>
+      <c r="B128" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C128" s="16" t="inlineStr">
         <is>
@@ -6193,14 +6113,16 @@
       </c>
       <c r="D128" s="16" t="inlineStr">
         <is>
-          <t>Finalizado por no show</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E128" s="17" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="F128" s="17" t="n">
-        <v>11.0</v>
+        <v>185.0</v>
+      </c>
+      <c r="F128" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G128" s="16" t="inlineStr">
         <is>
@@ -6209,7 +6131,7 @@
       </c>
       <c r="H128" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I128" s="18" t="inlineStr">
@@ -6219,18 +6141,20 @@
       </c>
       <c r="J128" s="16" t="inlineStr">
         <is>
-          <t>Agua purificadora los volcanes</t>
+          <t>99 MINUTOS</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="14" t="inlineStr">
         <is>
-          <t>dental art</t>
-        </is>
-      </c>
-      <c r="B129" s="15" t="n">
-        <v>0.0</v>
+          <t>RIVERLINE ERGONOMIC</t>
+        </is>
+      </c>
+      <c r="B129" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C129" s="16" t="inlineStr">
         <is>
@@ -6243,10 +6167,12 @@
         </is>
       </c>
       <c r="E129" s="17" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F129" s="17" t="n">
-        <v>5.0</v>
+        <v>122.0</v>
+      </c>
+      <c r="F129" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G129" s="16" t="inlineStr">
         <is>
@@ -6255,7 +6181,7 @@
       </c>
       <c r="H129" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I129" s="18" t="inlineStr">
@@ -6265,14 +6191,14 @@
       </c>
       <c r="J129" s="16" t="inlineStr">
         <is>
-          <t>dental Art</t>
+          <t>Riverline Ergonomic</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>IMPLEMENTACION NFS INTERNACIONAL MEXICO</t>
+          <t>CRRC MEXICO (RAILWAY MEXICO)</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
@@ -6282,16 +6208,16 @@
       </c>
       <c r="C130" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D130" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E130" s="17" t="n">
-        <v>67.0</v>
+        <v>200.0</v>
       </c>
       <c r="F130" s="17" t="inlineStr">
         <is>
@@ -6305,7 +6231,7 @@
       </c>
       <c r="H130" s="16" t="inlineStr">
         <is>
-          <t>Asistencia</t>
+          <t>Acceso; Externos</t>
         </is>
       </c>
       <c r="I130" s="18" t="inlineStr">
@@ -6315,22 +6241,24 @@
       </c>
       <c r="J130" s="16" t="inlineStr">
         <is>
-          <t>NFS MEXICO</t>
+          <t>CRRC Mexico</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="14" t="inlineStr">
         <is>
-          <t>Asistencia - E3 consultores - Biometricos</t>
-        </is>
-      </c>
-      <c r="B131" s="15" t="n">
-        <v>0.0</v>
+          <t>Comercializadora Valder (Aktiva Capital)</t>
+        </is>
+      </c>
+      <c r="B131" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C131" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D131" s="16" t="inlineStr">
@@ -6339,10 +6267,12 @@
         </is>
       </c>
       <c r="E131" s="17" t="n">
-        <v>326.0</v>
-      </c>
-      <c r="F131" s="17" t="n">
-        <v>403.0</v>
+        <v>484.0</v>
+      </c>
+      <c r="F131" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G131" s="16" t="inlineStr">
         <is>
@@ -6351,26 +6281,30 @@
       </c>
       <c r="H131" s="16" t="inlineStr">
         <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I131" s="18" t="n">
-        <v>45960.0</v>
+          <t>Asistencia</t>
+        </is>
+      </c>
+      <c r="I131" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J131" s="16" t="inlineStr">
         <is>
-          <t>E3 consultores</t>
+          <t>Comercializadora Valder (Aktiva Capital)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>EQUIPOS Y ACCESORIOS PARA GAS L.P. Y NATURAL</t>
-        </is>
-      </c>
-      <c r="B132" s="15" t="n">
-        <v>0.0</v>
+          <t>Ingeniería para Concretos</t>
+        </is>
+      </c>
+      <c r="B132" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C132" s="16" t="inlineStr">
         <is>
@@ -6383,10 +6317,12 @@
         </is>
       </c>
       <c r="E132" s="17" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="F132" s="17" t="n">
-        <v>11.0</v>
+        <v>100.0</v>
+      </c>
+      <c r="F132" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G132" s="16" t="inlineStr">
         <is>
@@ -6395,7 +6331,7 @@
       </c>
       <c r="H132" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I132" s="18" t="inlineStr">
@@ -6405,14 +6341,14 @@
       </c>
       <c r="J132" s="16" t="inlineStr">
         <is>
-          <t>Equipos y Accesorios para Gas L.P. y Natural</t>
+          <t>I.P.C.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="14" t="inlineStr">
         <is>
-          <t>Implementación Maquila ELEGANT FASHION</t>
+          <t>Productos lácteos la quinta</t>
         </is>
       </c>
       <c r="B133" s="15" t="inlineStr">
@@ -6422,16 +6358,16 @@
       </c>
       <c r="C133" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D133" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E133" s="17" t="n">
-        <v>65.0</v>
+        <v>400.0</v>
       </c>
       <c r="F133" s="17" t="inlineStr">
         <is>
@@ -6455,18 +6391,20 @@
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>NEFS</t>
+          <t>PRODUCTOS LACTEOS LA QUINTA</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>DKARLA</t>
-        </is>
-      </c>
-      <c r="B134" s="15" t="n">
-        <v>0.0</v>
+          <t>Haico HSC, HUC y DUO</t>
+        </is>
+      </c>
+      <c r="B134" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C134" s="16" t="inlineStr">
         <is>
@@ -6475,14 +6413,16 @@
       </c>
       <c r="D134" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E134" s="17" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="F134" s="17" t="n">
-        <v>26.0</v>
+        <v>80.0</v>
+      </c>
+      <c r="F134" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G134" s="16" t="inlineStr">
         <is>
@@ -6491,7 +6431,7 @@
       </c>
       <c r="H134" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Asistencia; Módulo Vacaciones</t>
         </is>
       </c>
       <c r="I134" s="18" t="inlineStr">
@@ -6501,34 +6441,38 @@
       </c>
       <c r="J134" s="16" t="inlineStr">
         <is>
-          <t>DKarla</t>
+          <t>Haico</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="14" t="inlineStr">
         <is>
-          <t>Implementación - Asistencia - Grupo Horizon</t>
-        </is>
-      </c>
-      <c r="B135" s="15" t="n">
-        <v>78.42</v>
+          <t>LIMPIEZA DOMESTICA SISTEMATIZADA KLIIN SA</t>
+        </is>
+      </c>
+      <c r="B135" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C135" s="16" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D135" s="16" t="inlineStr">
         <is>
-          <t>4. a) En Marcha Blanca (con pendientes)</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E135" s="17" t="n">
-        <v>615.0</v>
-      </c>
-      <c r="F135" s="17" t="n">
-        <v>331.0</v>
+        <v>118.0</v>
+      </c>
+      <c r="F135" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G135" s="16" t="inlineStr">
         <is>
@@ -6540,39 +6484,45 @@
           <t>Asistencia</t>
         </is>
       </c>
-      <c r="I135" s="18" t="n">
-        <v>46075.0</v>
+      <c r="I135" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="J135" s="16" t="inlineStr">
         <is>
-          <t>HORIZON AUTO LOGISTICS</t>
+          <t>Proveedor de Servicios In House Limpieza doméstica sistematizada</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>CITY WOK</t>
-        </is>
-      </c>
-      <c r="B136" s="15" t="n">
-        <v>0.0</v>
+          <t>Triturados agregados y construcciones pedregal</t>
+        </is>
+      </c>
+      <c r="B136" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C136" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D136" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E136" s="17" t="n">
-        <v>73.0</v>
-      </c>
-      <c r="F136" s="17" t="n">
-        <v>135.0</v>
+        <v>22.0</v>
+      </c>
+      <c r="F136" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G136" s="16" t="inlineStr">
         <is>
@@ -6581,7 +6531,7 @@
       </c>
       <c r="H136" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Asistencia</t>
         </is>
       </c>
       <c r="I136" s="18" t="inlineStr">
@@ -6591,34 +6541,38 @@
       </c>
       <c r="J136" s="16" t="inlineStr">
         <is>
-          <t>City wok</t>
+          <t>Triturados agregados y construcciones pedregal</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
-          <t>SERVICIOS DE MAQUILA Y MANIOBRA RENO</t>
-        </is>
-      </c>
-      <c r="B137" s="15" t="n">
-        <v>0.0</v>
+          <t>Converse (Accesos)</t>
+        </is>
+      </c>
+      <c r="B137" s="15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="C137" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D137" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E137" s="17" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="F137" s="17" t="n">
-        <v>22.0</v>
+        <v>900.0</v>
+      </c>
+      <c r="F137" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="G137" s="16" t="inlineStr">
         <is>
@@ -6637,14 +6591,14 @@
       </c>
       <c r="J137" s="16" t="inlineStr">
         <is>
-          <t>SERVICIOS DE MAQUILA Y MANIOBRA RENO</t>
+          <t>CONVERSE</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>Pleniahc</t>
+          <t>Colorland</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
@@ -6654,16 +6608,16 @@
       </c>
       <c r="C138" s="16" t="inlineStr">
         <is>
-          <t/>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D138" s="16" t="inlineStr">
         <is>
-          <t>Solicitud Rechazada</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="E138" s="17" t="n">
-        <v>12.0</v>
+        <v>100.0</v>
       </c>
       <c r="F138" s="17" t="inlineStr">
         <is>
@@ -6686,3266 +6640,6 @@
         </is>
       </c>
       <c r="J138" s="16" t="inlineStr">
-        <is>
-          <t>Pleniahc</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="14" t="inlineStr">
-        <is>
-          <t>TOUS COLOMBIA</t>
-        </is>
-      </c>
-      <c r="B139" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C139" s="16" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="D139" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E139" s="17" t="n">
-        <v>96.0</v>
-      </c>
-      <c r="F139" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G139" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H139" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I139" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J139" s="16" t="inlineStr">
-        <is>
-          <t>TOUS COLOMBIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="14" t="inlineStr">
-        <is>
-          <t>TOUS MEXICO</t>
-        </is>
-      </c>
-      <c r="B140" s="15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="C140" s="16" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="D140" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E140" s="17" t="n">
-        <v>449.0</v>
-      </c>
-      <c r="F140" s="17" t="n">
-        <v>449.0</v>
-      </c>
-      <c r="G140" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H140" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I140" s="18" t="n">
-        <v>45925.0</v>
-      </c>
-      <c r="J140" s="16" t="inlineStr">
-        <is>
-          <t>TOUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="14" t="inlineStr">
-        <is>
-          <t>DYA Manufacturas - Asistencia reloj biométrico</t>
-        </is>
-      </c>
-      <c r="B141" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C141" s="16" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="D141" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E141" s="17" t="n">
-        <v>326.0</v>
-      </c>
-      <c r="F141" s="17" t="n">
-        <v>377.0</v>
-      </c>
-      <c r="G141" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H141" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I141" s="18" t="n">
-        <v>45946.0</v>
-      </c>
-      <c r="J141" s="16" t="inlineStr">
-        <is>
-          <t>DYA MANUFACTURA</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="14" t="inlineStr">
-        <is>
-          <t>BROTHERS BEEF</t>
-        </is>
-      </c>
-      <c r="B142" s="15" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="C142" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D142" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E142" s="17" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="F142" s="17" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="G142" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H142" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I142" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J142" s="16" t="inlineStr">
-        <is>
-          <t>BROTHERS BEEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="14" t="inlineStr">
-        <is>
-          <t>MANGO AUDIO</t>
-        </is>
-      </c>
-      <c r="B143" s="15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="C143" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D143" s="16" t="inlineStr">
-        <is>
-          <t>6. Finalizada sin capacitación</t>
-        </is>
-      </c>
-      <c r="E143" s="17" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="F143" s="17" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="G143" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H143" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I143" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J143" s="16" t="inlineStr">
-        <is>
-          <t>MANGO AUDIO</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="14" t="inlineStr">
-        <is>
-          <t>INGENIERÍA GRUPO EMPRESARIAL ACTUAL</t>
-        </is>
-      </c>
-      <c r="B144" s="15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="C144" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D144" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E144" s="17" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F144" s="17" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="G144" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H144" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I144" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J144" s="16" t="inlineStr">
-        <is>
-          <t>Ingeniería Grupo Empresarial Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="14" t="inlineStr">
-        <is>
-          <t>IMPLEMENTACION METRO ASFALTOS</t>
-        </is>
-      </c>
-      <c r="B145" s="15" t="n">
-        <v>51.76</v>
-      </c>
-      <c r="C145" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D145" s="16" t="inlineStr">
-        <is>
-          <t>Finalizado por no show</t>
-        </is>
-      </c>
-      <c r="E145" s="17" t="n">
-        <v>93.0</v>
-      </c>
-      <c r="F145" s="17" t="n">
-        <v>93.0</v>
-      </c>
-      <c r="G145" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H145" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I145" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J145" s="16" t="inlineStr">
-        <is>
-          <t>METRO ASFALTOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="14" t="inlineStr">
-        <is>
-          <t>HOTELES GRAN CLASE SA DE CV</t>
-        </is>
-      </c>
-      <c r="B146" s="15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="C146" s="16" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="D146" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E146" s="17" t="n">
-        <v>56.0</v>
-      </c>
-      <c r="F146" s="17" t="n">
-        <v>62.0</v>
-      </c>
-      <c r="G146" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H146" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I146" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J146" s="16" t="inlineStr">
-        <is>
-          <t>Hoteles Gran Clase, SA de CV</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="14" t="inlineStr">
-        <is>
-          <t>SCR COMMUNICATION</t>
-        </is>
-      </c>
-      <c r="B147" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C147" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D147" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E147" s="17" t="n">
-        <v>74.0</v>
-      </c>
-      <c r="F147" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G147" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H147" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I147" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J147" s="16" t="inlineStr">
-        <is>
-          <t>SCR Communication</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="14" t="inlineStr">
-        <is>
-          <t>Hogan Lovells</t>
-        </is>
-      </c>
-      <c r="B148" s="15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="C148" s="16" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="D148" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E148" s="17" t="n">
-        <v>200.0</v>
-      </c>
-      <c r="F148" s="17" t="n">
-        <v>208.0</v>
-      </c>
-      <c r="G148" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H148" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I148" s="18" t="n">
-        <v>45868.0</v>
-      </c>
-      <c r="J148" s="16" t="inlineStr">
-        <is>
-          <t>Hogan Lovells</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="14" t="inlineStr">
-        <is>
-          <t>FUNDADORES BEACH CLUB AC</t>
-        </is>
-      </c>
-      <c r="B149" s="15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="C149" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D149" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E149" s="17" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="F149" s="17" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="G149" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H149" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I149" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J149" s="16" t="inlineStr">
-        <is>
-          <t>Fundadores</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="14" t="inlineStr">
-        <is>
-          <t>VIA URBANA (PACO APP)</t>
-        </is>
-      </c>
-      <c r="B150" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C150" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D150" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E150" s="17" t="n">
-        <v>57.0</v>
-      </c>
-      <c r="F150" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G150" s="16" t="inlineStr">
-        <is>
-          <t>PacoApp</t>
-        </is>
-      </c>
-      <c r="H150" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia; Integración Estándar</t>
-        </is>
-      </c>
-      <c r="I150" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J150" s="16" t="inlineStr">
-        <is>
-          <t>VIA URBANA</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="14" t="inlineStr">
-        <is>
-          <t>PRUEBA</t>
-        </is>
-      </c>
-      <c r="B151" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C151" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D151" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E151" s="17" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="F151" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G151" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H151" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I151" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J151" s="16" t="inlineStr">
-        <is>
-          <t>GeoVictoria Chile</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="14" t="inlineStr">
-        <is>
-          <t>Control de Asistencia</t>
-        </is>
-      </c>
-      <c r="B152" s="15" t="n">
-        <v>78.78</v>
-      </c>
-      <c r="C152" s="16" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="D152" s="16" t="inlineStr">
-        <is>
-          <t>Detenida</t>
-        </is>
-      </c>
-      <c r="E152" s="17" t="n">
-        <v>622.0</v>
-      </c>
-      <c r="F152" s="17" t="n">
-        <v>643.0</v>
-      </c>
-      <c r="G152" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H152" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I152" s="18" t="n">
-        <v>45946.0</v>
-      </c>
-      <c r="J152" s="16" t="inlineStr">
-        <is>
-          <t>Los Cinco Soles</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="14" t="inlineStr">
-        <is>
-          <t>Pensiones Libertad</t>
-        </is>
-      </c>
-      <c r="B153" s="15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="C153" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D153" s="16" t="inlineStr">
-        <is>
-          <t>Finalizado por no show</t>
-        </is>
-      </c>
-      <c r="E153" s="17" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F153" s="17" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="G153" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H153" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I153" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J153" s="16" t="inlineStr">
-        <is>
-          <t>Pensiones libertad</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="14" t="inlineStr">
-        <is>
-          <t>Transportes Wong Implementacion</t>
-        </is>
-      </c>
-      <c r="B154" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C154" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D154" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E154" s="17" t="n">
-        <v>122.0</v>
-      </c>
-      <c r="F154" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G154" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H154" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I154" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J154" s="16" t="inlineStr">
-        <is>
-          <t>TRANSPORTES WONG DE LA TORRE</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="14" t="inlineStr">
-        <is>
-          <t>Transportes Wong</t>
-        </is>
-      </c>
-      <c r="B155" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C155" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D155" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E155" s="17" t="n">
-        <v>122.0</v>
-      </c>
-      <c r="F155" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G155" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H155" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I155" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J155" s="16" t="inlineStr">
-        <is>
-          <t>TRANSPORTES WONG DE LA TORRE</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="14" t="inlineStr">
-        <is>
-          <t>Asistencia (Liberación puerta) - Vacaciones - Hogan Lovells</t>
-        </is>
-      </c>
-      <c r="B156" s="15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="C156" s="16" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="D156" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E156" s="17" t="n">
-        <v>208.0</v>
-      </c>
-      <c r="F156" s="17" t="n">
-        <v>208.0</v>
-      </c>
-      <c r="G156" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H156" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I156" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J156" s="16" t="inlineStr">
-        <is>
-          <t>Hogan Lovells</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="14" t="inlineStr">
-        <is>
-          <t>Asistencia (Liberación puerta) - Vacaciones - Hogan Lovells</t>
-        </is>
-      </c>
-      <c r="B157" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C157" s="16" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="D157" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E157" s="17" t="n">
-        <v>208.0</v>
-      </c>
-      <c r="F157" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G157" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H157" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I157" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J157" s="16" t="inlineStr">
-        <is>
-          <t>Hogan Lovells</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="14" t="inlineStr">
-        <is>
-          <t>FREEDOMPOP</t>
-        </is>
-      </c>
-      <c r="B158" s="15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="C158" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D158" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E158" s="17" t="n">
-        <v>39.0</v>
-      </c>
-      <c r="F158" s="17" t="n">
-        <v>41.0</v>
-      </c>
-      <c r="G158" s="16" t="inlineStr">
-        <is>
-          <t>Buk</t>
-        </is>
-      </c>
-      <c r="H158" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I158" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J158" s="16" t="inlineStr">
-        <is>
-          <t>FREEDOMPOP MEXICO SA</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="14" t="inlineStr">
-        <is>
-          <t>Accesos Softys</t>
-        </is>
-      </c>
-      <c r="B159" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C159" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D159" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E159" s="17" t="n">
-        <v>500.0</v>
-      </c>
-      <c r="F159" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G159" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H159" s="16" t="inlineStr">
-        <is>
-          <t>Externos; Gestor Documental</t>
-        </is>
-      </c>
-      <c r="I159" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J159" s="16" t="inlineStr">
-        <is>
-          <t>Softys México</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="14" t="inlineStr">
-        <is>
-          <t>MAFERSA - ASISTENCIA</t>
-        </is>
-      </c>
-      <c r="B160" s="15" t="n">
-        <v>36.61</v>
-      </c>
-      <c r="C160" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D160" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E160" s="17" t="n">
-        <v>126.0</v>
-      </c>
-      <c r="F160" s="17" t="n">
-        <v>122.0</v>
-      </c>
-      <c r="G160" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H160" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I160" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J160" s="16" t="inlineStr">
-        <is>
-          <t>Desarrollos MAFERSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="14" t="inlineStr">
-        <is>
-          <t>ALBERCAS VENZAR</t>
-        </is>
-      </c>
-      <c r="B161" s="15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="C161" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D161" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E161" s="17" t="n">
-        <v>53.0</v>
-      </c>
-      <c r="F161" s="17" t="n">
-        <v>65.0</v>
-      </c>
-      <c r="G161" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H161" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I161" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J161" s="16" t="inlineStr">
-        <is>
-          <t>Albercas Venzarr</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="14" t="inlineStr">
-        <is>
-          <t>CMPC - Implementación Asistencia + Comedor + Vacaciones + Dashboard BI</t>
-        </is>
-      </c>
-      <c r="B162" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C162" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D162" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E162" s="17" t="n">
-        <v>350.0</v>
-      </c>
-      <c r="F162" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G162" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H162" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia; Comedor; Dashboard; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I162" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J162" s="16" t="inlineStr">
-        <is>
-          <t>CMPC México</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="14" t="inlineStr">
-        <is>
-          <t>NAYARTA ENTERTAIMENT ASISTENCIA</t>
-        </is>
-      </c>
-      <c r="B163" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C163" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D163" s="16" t="inlineStr">
-        <is>
-          <t>Finalizado sin uso de plataforma</t>
-        </is>
-      </c>
-      <c r="E163" s="17" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F163" s="17" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="G163" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H163" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I163" s="18" t="n">
-        <v>45827.0</v>
-      </c>
-      <c r="J163" s="16" t="inlineStr">
-        <is>
-          <t>NAYARTA ENTERTAINMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="14" t="inlineStr">
-        <is>
-          <t>GRUPO EMPRESARIAL LA PIRAMIDE</t>
-        </is>
-      </c>
-      <c r="B164" s="15" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="C164" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D164" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E164" s="17" t="n">
-        <v>163.0</v>
-      </c>
-      <c r="F164" s="17" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="G164" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H164" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I164" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J164" s="16" t="inlineStr">
-        <is>
-          <t>Grupo empresarial la piramide</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="14" t="inlineStr">
-        <is>
-          <t>Implementación Grupo JULIO- Asistencia</t>
-        </is>
-      </c>
-      <c r="B165" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C165" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D165" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E165" s="17" t="n">
-        <v>1300.0</v>
-      </c>
-      <c r="F165" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G165" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H165" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I165" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J165" s="16" t="inlineStr">
-        <is>
-          <t>Grupo JULIO - Asistencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="14" t="inlineStr">
-        <is>
-          <t>Limver</t>
-        </is>
-      </c>
-      <c r="B166" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C166" s="16" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="D166" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E166" s="17" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F166" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G166" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H166" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I166" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J166" s="16" t="inlineStr">
-        <is>
-          <t>HOC EST BONUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="14" t="inlineStr">
-        <is>
-          <t>Asistencia-EB7</t>
-        </is>
-      </c>
-      <c r="B167" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C167" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D167" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E167" s="17" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F167" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G167" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H167" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I167" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J167" s="16" t="inlineStr">
-        <is>
-          <t>EB7</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="14" t="inlineStr">
-        <is>
-          <t>Asistencia-EB7</t>
-        </is>
-      </c>
-      <c r="B168" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C168" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D168" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E168" s="17" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F168" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G168" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H168" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I168" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J168" s="16" t="inlineStr">
-        <is>
-          <t>EB7</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="14" t="inlineStr">
-        <is>
-          <t>Serintra - Accesos</t>
-        </is>
-      </c>
-      <c r="B169" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C169" s="16" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="D169" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E169" s="17" t="n">
-        <v>35.0</v>
-      </c>
-      <c r="F169" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G169" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H169" s="16" t="inlineStr">
-        <is>
-          <t>Acceso</t>
-        </is>
-      </c>
-      <c r="I169" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J169" s="16" t="inlineStr">
-        <is>
-          <t>SERINTRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="14" t="inlineStr">
-        <is>
-          <t>Implementación Modulo de Vacaciones</t>
-        </is>
-      </c>
-      <c r="B170" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C170" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D170" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E170" s="17" t="n">
-        <v>104.0</v>
-      </c>
-      <c r="F170" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G170" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H170" s="16" t="inlineStr">
-        <is>
-          <t>Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I170" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J170" s="16" t="inlineStr">
-        <is>
-          <t>Transmal</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="14" t="inlineStr">
-        <is>
-          <t>Rena comercializadora - WhatsApp</t>
-        </is>
-      </c>
-      <c r="B171" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C171" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D171" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E171" s="17" t="n">
-        <v>538.0</v>
-      </c>
-      <c r="F171" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G171" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H171" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I171" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J171" s="16" t="inlineStr">
-        <is>
-          <t>Rena Comercializadora</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="14" t="inlineStr">
-        <is>
-          <t>Módulo de Vacaciones</t>
-        </is>
-      </c>
-      <c r="B172" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C172" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D172" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E172" s="17" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="F172" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G172" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H172" s="16" t="inlineStr">
-        <is>
-          <t>Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I172" s="18" t="n">
-        <v>45743.0</v>
-      </c>
-      <c r="J172" s="16" t="inlineStr">
-        <is>
-          <t>Transmal</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="14" t="inlineStr">
-        <is>
-          <t>Reimplementación Vanity</t>
-        </is>
-      </c>
-      <c r="B173" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C173" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D173" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E173" s="17" t="n">
-        <v>500.0</v>
-      </c>
-      <c r="F173" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G173" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H173" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I173" s="18" t="n">
-        <v>45701.0</v>
-      </c>
-      <c r="J173" s="16" t="inlineStr">
-        <is>
-          <t>Vanity</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="14" t="inlineStr">
-        <is>
-          <t>MKP Agrícola</t>
-        </is>
-      </c>
-      <c r="B174" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C174" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D174" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E174" s="17" t="n">
-        <v>47.0</v>
-      </c>
-      <c r="F174" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G174" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H174" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I174" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J174" s="16" t="inlineStr">
-        <is>
-          <t>MKP Agricola MX</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="14" t="inlineStr">
-        <is>
-          <t>VEDAT DE MEXICO SA DE CV (asistencia)</t>
-        </is>
-      </c>
-      <c r="B175" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C175" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D175" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E175" s="17" t="n">
-        <v>53.0</v>
-      </c>
-      <c r="F175" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G175" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H175" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I175" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J175" s="16" t="inlineStr">
-        <is>
-          <t>VEDAT DE MEXICO SA de CV</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="14" t="inlineStr">
-        <is>
-          <t>Britt Shops Retail Mexico MTE</t>
-        </is>
-      </c>
-      <c r="B176" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C176" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D176" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E176" s="17" t="n">
-        <v>90.0</v>
-      </c>
-      <c r="F176" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G176" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H176" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia; Formas de Pago</t>
-        </is>
-      </c>
-      <c r="I176" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J176" s="16" t="inlineStr">
-        <is>
-          <t>Morpho Travel Mexico</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="14" t="inlineStr">
-        <is>
-          <t>Servicios Comerciales del Sur MTE</t>
-        </is>
-      </c>
-      <c r="B177" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C177" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D177" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E177" s="17" t="n">
-        <v>200.0</v>
-      </c>
-      <c r="F177" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G177" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H177" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia; Formas de Pago</t>
-        </is>
-      </c>
-      <c r="I177" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J177" s="16" t="inlineStr">
-        <is>
-          <t>Morpho Travel Mexico</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="14" t="inlineStr">
-        <is>
-          <t>VEDAT DE MEXICO SA DE CV (asistencia)</t>
-        </is>
-      </c>
-      <c r="B178" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C178" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D178" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E178" s="17" t="n">
-        <v>53.0</v>
-      </c>
-      <c r="F178" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G178" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H178" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I178" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J178" s="16" t="inlineStr">
-        <is>
-          <t>VEDAT DE MEXICO SA de CV</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="14" t="inlineStr">
-        <is>
-          <t>INMOBILIARIA INMOBICO SA DE CV (control de asistencia)</t>
-        </is>
-      </c>
-      <c r="B179" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C179" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D179" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E179" s="17" t="n">
-        <v>39.0</v>
-      </c>
-      <c r="F179" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G179" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H179" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I179" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J179" s="16" t="inlineStr">
-        <is>
-          <t>INMOBILIARIA INMOBICO SA DE CV</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="14" t="inlineStr">
-        <is>
-          <t>PACADA - Asistencia</t>
-        </is>
-      </c>
-      <c r="B180" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C180" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D180" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E180" s="17" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F180" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G180" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H180" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I180" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J180" s="16" t="inlineStr">
-        <is>
-          <t>PACADA</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="14" t="inlineStr">
-        <is>
-          <t>TOUS</t>
-        </is>
-      </c>
-      <c r="B181" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C181" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D181" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E181" s="17" t="n">
-        <v>560.0</v>
-      </c>
-      <c r="F181" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G181" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H181" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I181" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J181" s="16" t="inlineStr">
-        <is>
-          <t>TOUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="14" t="inlineStr">
-        <is>
-          <t>TOUS</t>
-        </is>
-      </c>
-      <c r="B182" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C182" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D182" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E182" s="17" t="n">
-        <v>560.0</v>
-      </c>
-      <c r="F182" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G182" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H182" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I182" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J182" s="16" t="inlineStr">
-        <is>
-          <t>TOUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="14" t="inlineStr">
-        <is>
-          <t>Office Max</t>
-        </is>
-      </c>
-      <c r="B183" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C183" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D183" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E183" s="17" t="n">
-        <v>2000.0</v>
-      </c>
-      <c r="F183" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G183" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H183" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I183" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J183" s="16" t="inlineStr">
-        <is>
-          <t>Office Max</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="14" t="inlineStr">
-        <is>
-          <t>Puebla Agricola - Control de asistencia</t>
-        </is>
-      </c>
-      <c r="B184" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C184" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D184" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E184" s="17" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F184" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G184" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H184" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I184" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J184" s="16" t="inlineStr">
-        <is>
-          <t>Puebla Agrícola</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="14" t="inlineStr">
-        <is>
-          <t>Modulo Vacaciones - Grupo REM</t>
-        </is>
-      </c>
-      <c r="B185" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C185" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D185" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E185" s="17" t="n">
-        <v>170.0</v>
-      </c>
-      <c r="F185" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G185" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H185" s="16" t="inlineStr">
-        <is>
-          <t>Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I185" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J185" s="16" t="inlineStr">
-        <is>
-          <t>COMEX MEXICALI</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="14" t="inlineStr">
-        <is>
-          <t>Implementación Control de Asistencia Laboratorio SantaMaria</t>
-        </is>
-      </c>
-      <c r="B186" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C186" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D186" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E186" s="17" t="n">
-        <v>560.0</v>
-      </c>
-      <c r="F186" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G186" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H186" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I186" s="18" t="n">
-        <v>45680.0</v>
-      </c>
-      <c r="J186" s="16" t="inlineStr">
-        <is>
-          <t>Laboratorio Santamaría</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="14" t="inlineStr">
-        <is>
-          <t>Similares Bremmer</t>
-        </is>
-      </c>
-      <c r="B187" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C187" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D187" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E187" s="17" t="n">
-        <v>260.0</v>
-      </c>
-      <c r="F187" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G187" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H187" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I187" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J187" s="16" t="inlineStr">
-        <is>
-          <t>Simi del norte - Daniel Bremer</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="14" t="inlineStr">
-        <is>
-          <t>Marel México</t>
-        </is>
-      </c>
-      <c r="B188" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C188" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D188" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E188" s="17" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="F188" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G188" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H188" s="16" t="inlineStr">
-        <is>
-          <t>Formas de Pago</t>
-        </is>
-      </c>
-      <c r="I188" s="18" t="n">
-        <v>45715.0</v>
-      </c>
-      <c r="J188" s="16" t="inlineStr">
-        <is>
-          <t>MAREL MEXICO</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="14" t="inlineStr">
-        <is>
-          <t>Marcaje WA - Siramper</t>
-        </is>
-      </c>
-      <c r="B189" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C189" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D189" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E189" s="17" t="n">
-        <v>900.0</v>
-      </c>
-      <c r="F189" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G189" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H189" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I189" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J189" s="16" t="inlineStr">
-        <is>
-          <t>SIRAMPER</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="14" t="inlineStr">
-        <is>
-          <t>Netafim MM</t>
-        </is>
-      </c>
-      <c r="B190" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C190" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D190" s="16" t="inlineStr">
-        <is>
-          <t>Solicitud Rechazada</t>
-        </is>
-      </c>
-      <c r="E190" s="17" t="n">
-        <v>220.0</v>
-      </c>
-      <c r="F190" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G190" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H190" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia; Dashboard; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I190" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J190" s="16" t="inlineStr">
-        <is>
-          <t>Netafim Manufacturing México</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="14" t="inlineStr">
-        <is>
-          <t>DDVC</t>
-        </is>
-      </c>
-      <c r="B191" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C191" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D191" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E191" s="17" t="n">
-        <v>305.0</v>
-      </c>
-      <c r="F191" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G191" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H191" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I191" s="18" t="n">
-        <v>45573.0</v>
-      </c>
-      <c r="J191" s="16" t="inlineStr">
-        <is>
-          <t>DEPOSITO DENTAL VILLA DE CORTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="14" t="inlineStr">
-        <is>
-          <t>Universidad Tecnológica de Querétaro</t>
-        </is>
-      </c>
-      <c r="B192" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C192" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D192" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E192" s="17" t="n">
-        <v>561.0</v>
-      </c>
-      <c r="F192" s="17" t="n">
-        <v>512.0</v>
-      </c>
-      <c r="G192" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H192" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I192" s="18" t="n">
-        <v>45722.0</v>
-      </c>
-      <c r="J192" s="16" t="inlineStr">
-        <is>
-          <t>UTEQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="14" t="inlineStr">
-        <is>
-          <t>PAN AMERICAN SILVER</t>
-        </is>
-      </c>
-      <c r="B193" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C193" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D193" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E193" s="17" t="n">
-        <v>1185.0</v>
-      </c>
-      <c r="F193" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G193" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H193" s="16" t="inlineStr">
-        <is>
-          <t>Comedor</t>
-        </is>
-      </c>
-      <c r="I193" s="18" t="n">
-        <v>45564.0</v>
-      </c>
-      <c r="J193" s="16" t="inlineStr">
-        <is>
-          <t>PAN AMERICAN SILVER</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="14" t="inlineStr">
-        <is>
-          <t>ANTROMEX</t>
-        </is>
-      </c>
-      <c r="B194" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C194" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D194" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E194" s="17" t="n">
-        <v>136.0</v>
-      </c>
-      <c r="F194" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G194" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H194" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I194" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J194" s="16" t="inlineStr">
-        <is>
-          <t>ANTROMEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="14" t="inlineStr">
-        <is>
-          <t>99 MINUTOS MX</t>
-        </is>
-      </c>
-      <c r="B195" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C195" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D195" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E195" s="17" t="n">
-        <v>185.0</v>
-      </c>
-      <c r="F195" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G195" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H195" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I195" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J195" s="16" t="inlineStr">
-        <is>
-          <t>99 MINUTOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="14" t="inlineStr">
-        <is>
-          <t>RIVERLINE ERGONOMIC</t>
-        </is>
-      </c>
-      <c r="B196" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C196" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D196" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E196" s="17" t="n">
-        <v>122.0</v>
-      </c>
-      <c r="F196" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G196" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H196" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I196" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J196" s="16" t="inlineStr">
-        <is>
-          <t>Riverline Ergonomic</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="14" t="inlineStr">
-        <is>
-          <t>CRRC MEXICO (RAILWAY MEXICO)</t>
-        </is>
-      </c>
-      <c r="B197" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C197" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D197" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E197" s="17" t="n">
-        <v>200.0</v>
-      </c>
-      <c r="F197" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G197" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H197" s="16" t="inlineStr">
-        <is>
-          <t>Acceso; Externos</t>
-        </is>
-      </c>
-      <c r="I197" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J197" s="16" t="inlineStr">
-        <is>
-          <t>CRRC Mexico</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="14" t="inlineStr">
-        <is>
-          <t>Comercializadora Valder (Aktiva Capital)</t>
-        </is>
-      </c>
-      <c r="B198" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C198" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D198" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E198" s="17" t="n">
-        <v>484.0</v>
-      </c>
-      <c r="F198" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G198" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H198" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I198" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J198" s="16" t="inlineStr">
-        <is>
-          <t>Comercializadora Valder (Aktiva Capital)</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="14" t="inlineStr">
-        <is>
-          <t>Ingeniería para Concretos</t>
-        </is>
-      </c>
-      <c r="B199" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C199" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D199" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E199" s="17" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="F199" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G199" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H199" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I199" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J199" s="16" t="inlineStr">
-        <is>
-          <t>I.P.C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="14" t="inlineStr">
-        <is>
-          <t>Productos lácteos la quinta</t>
-        </is>
-      </c>
-      <c r="B200" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C200" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D200" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E200" s="17" t="n">
-        <v>400.0</v>
-      </c>
-      <c r="F200" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G200" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H200" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I200" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J200" s="16" t="inlineStr">
-        <is>
-          <t>PRODUCTOS LACTEOS LA QUINTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="14" t="inlineStr">
-        <is>
-          <t>Haico HSC, HUC y DUO</t>
-        </is>
-      </c>
-      <c r="B201" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C201" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D201" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E201" s="17" t="n">
-        <v>80.0</v>
-      </c>
-      <c r="F201" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G201" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H201" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia; Módulo Vacaciones</t>
-        </is>
-      </c>
-      <c r="I201" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J201" s="16" t="inlineStr">
-        <is>
-          <t>Haico</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="14" t="inlineStr">
-        <is>
-          <t>LIMPIEZA DOMESTICA SISTEMATIZADA KLIIN SA</t>
-        </is>
-      </c>
-      <c r="B202" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C202" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D202" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E202" s="17" t="n">
-        <v>118.0</v>
-      </c>
-      <c r="F202" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G202" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H202" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I202" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J202" s="16" t="inlineStr">
-        <is>
-          <t>Proveedor de Servicios In House Limpieza doméstica sistematizada</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="14" t="inlineStr">
-        <is>
-          <t>Triturados agregados y construcciones pedregal</t>
-        </is>
-      </c>
-      <c r="B203" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C203" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D203" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E203" s="17" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="F203" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G203" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H203" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I203" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J203" s="16" t="inlineStr">
-        <is>
-          <t>Triturados agregados y construcciones pedregal</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="14" t="inlineStr">
-        <is>
-          <t>Converse (Accesos)</t>
-        </is>
-      </c>
-      <c r="B204" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C204" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D204" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E204" s="17" t="n">
-        <v>900.0</v>
-      </c>
-      <c r="F204" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G204" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H204" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I204" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J204" s="16" t="inlineStr">
-        <is>
-          <t>CONVERSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="14" t="inlineStr">
-        <is>
-          <t>Colorland</t>
-        </is>
-      </c>
-      <c r="B205" s="15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C205" s="16" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D205" s="16" t="inlineStr">
-        <is>
-          <t>Abandono</t>
-        </is>
-      </c>
-      <c r="E205" s="17" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="F205" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G205" s="16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H205" s="16" t="inlineStr">
-        <is>
-          <t>Asistencia</t>
-        </is>
-      </c>
-      <c r="I205" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J205" s="16" t="inlineStr">
         <is>
           <t>COLORLAND</t>
         </is>
